--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0019.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0019.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Có Companions sẽ giúp thực hiện Điều Ước của người khác dễ dàng hơn.</t>
+          <t>Có Đồng Hành bên cạnh sẽ giúp thực hiện Điều Ước của người khác dễ dàng hơn.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Có Companions sẽ giúp thực hiện Điều Ước của người khác dễ dàng hơn.</t>
+          <t>Có Đồng Hành bên cạnh sẽ giúp thực hiện Điều Ước của người khác dễ dàng hơn.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Những Điều Ước khác nhau yêu cầu chỉ số khác nhau để xử lý.</t>
+          <t>Mỗi Điều Ước đòi hỏi những chỉ số khác nhau để xử lý.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Những Điều Ước khác nhau yêu cầu chỉ số khác nhau để xử lý.</t>
+          <t>Mỗi Điều Ước đòi hỏi những chỉ số khác nhau để xử lý.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Những Điều Ước khác nhau yêu cầu chỉ số khác nhau để xử lý.</t>
+          <t>Mỗi Điều Ước đòi hỏi những chỉ số khác nhau để xử lý.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Chỉ số đề xuất càng cao, việc hoàn thành Điều Ước càng dễ dàng.</t>
+          <t>Chỉ số đề xuất càng cao, việc hoàn thành Ước Nguyện càng dễ dàng.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Chỉ số đề xuất càng cao, việc hoàn thành Điều Ước càng dễ dàng.</t>
+          <t>Chỉ số đề xuất càng cao, việc hoàn thành Ước Nguyện càng dễ dàng.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Chỉ số đề xuất càng cao, việc hoàn thành Điều Ước càng dễ dàng.</t>
+          <t>Chỉ số đề xuất càng cao, việc hoàn thành Ước Nguyện càng dễ dàng.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Chạm khi bạn đã sẵn sàng khởi hành.</t>
+          <t>Chạm khi bạn đã sẵn sàng lên đường.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>{0} Nhấn khi bạn đã sẵn sàng khởi hành.</t>
+          <t>Nhấn khi đã sẵn sàng xuất phát.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Chạm khi bạn đã sẵn sàng khởi hành.</t>
+          <t>Chạm khi bạn đã sẵn sàng lên đường.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Xếp Hạng Wish càng cao, Funds nhận được càng nhiều.</t>
+          <t>Xếp hạng Ước Nguyện càng cao, số Tài Nguyên ngươi nhận được càng nhiều.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Xếp Hạng Wish càng cao, Funds nhận được càng nhiều.</t>
+          <t>Xếp hạng Ước Nguyện càng cao, số Tài Nguyên ngươi nhận được càng nhiều.</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Xếp Hạng Wish càng cao, Funds nhận được càng nhiều.</t>
+          <t>Xếp hạng Ước Nguyện càng cao, số Tài Nguyên ngươi nhận được càng nhiều.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Tổng điểm dựa trên chỉ số sẽ quyết định xếp hạng Wish Ratings.</t>
+          <t>Tổng điểm đạt được dựa trên chỉ số sẽ quyết định Xếp Hạng Nguyện Ước.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Tổng điểm dựa trên chỉ số sẽ quyết định xếp hạng Wish Ratings.</t>
+          <t>Tổng điểm đạt được dựa trên chỉ số sẽ quyết định Xếp Hạng Nguyện Ước.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Tổng điểm dựa trên chỉ số sẽ quyết định xếp hạng Wish Ratings.</t>
+          <t>Tổng điểm đạt được dựa trên chỉ số sẽ quyết định Xếp Hạng Nguyện Ước.</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Sau khi xây dựng quầy hàng, cậu có thể mời thêm Companion. Hãy thử xem nhé!</t>
+          <t>Sau khi xây dựng các gian hàng, ngươi có thể mời thêm Đồng Hành. Hãy thử xem nào!</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>{0} Sau khi xây dựng quầy hàng, bạn có thể mời thêm Companions. Hãy thử xem nào!</t>
+          <t>Sau khi xây dựng quầy hàng, cậu có thể mời thêm Đồng Hành. Vào xem thử đi!</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Sau khi xây dựng quầy hàng, cậu có thể mời thêm Companion. Hãy thử xem nhé!</t>
+          <t>Sau khi xây dựng các gian hàng, ngươi có thể mời thêm Đồng Hành. Hãy thử xem nào!</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Chạm vào đây để xem tất cả Moments đã mở khóa.</t>
+          <t>Chạm vào đây để xem tất cả Khoảnh Khắc đã mở khóa.</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Chạm vào đây để xem tất cả Moments đã mở khóa.</t>
+          <t>Chạm vào đây để xem tất cả Khoảnh Khắc đã mở khóa.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Chạm vào đây để xem tất cả Moments đã mở khóa.</t>
+          <t>Chạm vào đây để xem tất cả Khoảnh Khắc đã mở khóa.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ để mời Companions tương ứng, đồng thời nhận được một lượng lớn Preparation Credits.</t>
+          <t>Hoàn thành nhiệm vụ để mời các Đồng Hành tương ứng, đồng thời nhận được một lượng lớn Tín Dụng Chuẩn Bị.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ để mời Companions tương ứng, đồng thời nhận được một lượng lớn Preparation Credits.</t>
+          <t>Hoàn thành nhiệm vụ để mời các Đồng Hành tương ứng, đồng thời nhận được một lượng lớn Tín Dụng Chuẩn Bị.</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ để mời Companions tương ứng, đồng thời nhận được một lượng lớn Preparation Credits.</t>
+          <t>Hoàn thành nhiệm vụ để mời các Đồng Hành tương ứng, đồng thời nhận được một lượng lớn Tín Dụng Chuẩn Bị.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Chạm vào Companions để xem chỉ số chi tiết.</t>
+          <t>Nhấn vào Đồng Hành để xem thông số chi tiết của họ.</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>{0} Chạm vào Đồng hành để xem thông số chi tiết.</t>
+          <t>Nhấn vào Đồng Hành để xem chỉ số chi tiết.</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Chạm vào Companions để xem chỉ số chi tiết.</t>
+          <t>Nhấn vào Đồng Hành để xem thông số chi tiết của họ.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ tương ứng để mời Companions.</t>
+          <t>Hoàn thành các nhiệm vụ tương ứng để mời Đồng Hành.</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ tương ứng để mời Companions.</t>
+          <t>Hoàn thành các nhiệm vụ tương ứng để mời Đồng Hành.</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ tương ứng để mời Companions.</t>
+          <t>Hoàn thành các nhiệm vụ tương ứng để mời Đồng Hành.</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Khi chỉ số Đồng Hành tăng, Đánh Giá Nguyện Vọng cũng sẽ tăng theo.</t>
+          <t>Khi chỉ số Đồng Hành tăng lên, Đánh Giá Nguyện Ước cũng sẽ tăng theo.</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Khi chỉ số Đồng Hành tăng, Đánh Giá Nguyện Vọng cũng sẽ tăng theo.</t>
+          <t>Khi chỉ số Đồng Hành tăng lên, Đánh Giá Nguyện Ước cũng sẽ tăng theo.</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Khi chỉ số Đồng Hành tăng, Đánh Giá Nguyện Vọng cũng sẽ tăng theo.</t>
+          <t>Khi chỉ số Đồng Hành tăng lên, Đánh Giá Nguyện Ước cũng sẽ tăng theo.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Dành thời gian với Companions để tăng mạnh Cấp Độ Gắn Kết và chỉ số của họ.</t>
+          <t>Dành thời gian bên Cộng Sự để tăng mạnh Cấp Độ Gắn Kết và chỉ số của họ.</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Dành thời gian với Companions để tăng mạnh Cấp Độ Gắn Kết và chỉ số của họ.</t>
+          <t>Dành thời gian bên Cộng Sự để tăng mạnh Cấp Độ Gắn Kết và chỉ số của họ.</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Dành thời gian với Companions để tăng mạnh Cấp Độ Gắn Kết và chỉ số của họ.</t>
+          <t>Dành thời gian bên Cộng Sự để tăng mạnh Cấp Độ Gắn Kết và chỉ số của họ.</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Đồng hành có thể trải qua khoảnh khắc "Eureka" và dẫn đến kết quả bất ngờ.</t>
+          <t>Đồng đội có thể trải qua khoảnh khắc "Eureka" và tạo ra kết quả bất ngờ.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Đồng hành có thể trải qua khoảnh khắc "Eureka" và dẫn đến kết quả bất ngờ.</t>
+          <t>Đồng đội có thể trải qua khoảnh khắc "Eureka" và tạo ra kết quả bất ngờ.</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Đồng hành có thể trải qua khoảnh khắc "Eureka" và dẫn đến kết quả bất ngờ.</t>
+          <t>Đồng đội có thể trải qua khoảnh khắc "Eureka" và tạo ra kết quả bất ngờ.</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Nhấn để xem chi tiết nhiệm vụ đã mở khóa.</t>
+          <t>Chạm để xem chi tiết nhiệm vụ đã mở khóa.</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>{0} Nhấn để xem chi tiết nhiệm vụ đã mở khóa.</t>
+          <t>Nhấn {0} để xem chi tiết nhiệm vụ đã mở khóa.</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Nhấn để xem chi tiết nhiệm vụ đã mở khóa.</t>
+          <t>Chạm để xem chi tiết nhiệm vụ đã mở khóa.</t>
         </is>
       </c>
     </row>
@@ -3435,8 +3435,8 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Nhấn {0} để &lt;color=#8c7e51&gt;khóa camera&lt;/color&gt;.
-Nhấn lại để hủy.</t>
+          <t>Chạm {0} để &lt;color=#8c7e51&gt;khóa camera&lt;/color&gt;.
+Chạm lại để hủy.</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
       <c r="M47" t="inlineStr">
         <is>
           <t>Chạm để &lt;color=#8c7e51&gt;khóa camera&lt;/color&gt;.
-Chạm lại để hủy.</t>
+Chạm lần nữa để hủy.</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Thu thập Wish Tag để tương tác với Đồng Hành trong Time Together.</t>
+          <t>Thu thập Thẻ Nguyện Ước để tương tác với Đồng Hành trong *Thời Gian Bên Nhau*.</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>{0} Thu thập Wish Tag để tương tác với Companions trong Thời Gian Bên Nhau.</t>
+          <t>Thu thập Wish Tags để tương tác với các Đồng Hành trong Time Together.</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Thu thập Wish Tag để tương tác với Đồng Hành trong Time Together.</t>
+          <t>Thu thập Thẻ Nguyện Ước để tương tác với Đồng Hành trong *Thời Gian Bên Nhau*.</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Chọn Resonator đồng hành đã mở khóa.</t>
+          <t>Chọn Cộng Hưởng Giả đã mở khóa.</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Chọn Resonator đồng hành đã mở khóa.</t>
+          <t>Chọn Cộng Hưởng Giả đã mở khóa.</t>
         </is>
       </c>
     </row>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Chọn Resonator đồng hành đã mở khóa.</t>
+          <t>Chọn Cộng Hưởng Giả đã mở khóa.</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Nâng cấp quầy hàng có thể tăng Độ Nổi Tiếng và thu nhập từ Điều Ước.</t>
+          <t>Nâng cấp gian hàng có thể tăng Độ Nổi Tiếng và thu nhập từ Điều Ước.</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>{0} Nâng cấp quầy hàng có thể tăng Độ Nổi Tiếng và thu nhập từ Wishes.</t>
+          <t>{0} Nâng cấp gian hàng sẽ tăng Độ Nổi Tiếng và thu nhập từ Điều Ước.</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Nâng cấp quầy hàng có thể tăng Độ Nổi Tiếng và thu nhập từ Điều Ước.</t>
+          <t>Nâng cấp gian hàng có thể tăng Độ Nổi Tiếng và thu nhập từ Điều Ước.</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Chọn một quầy có thể nâng cấp.</t>
+          <t>Chọn quầy hàng có thể nâng cấp.</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Chọn một quầy có thể nâng cấp.</t>
+          <t>Chọn quầy hàng có thể nâng cấp.</t>
         </is>
       </c>
     </row>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Chọn một quầy có thể nâng cấp.</t>
+          <t>Chọn quầy hàng có thể nâng cấp.</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Bây giờ, hãy thử nâng cấp một quầy hàng nào!</t>
+          <t>Giờ thì thử nâng cấp một gian hàng nào!</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Bây giờ {0}, hãy thử nâng cấp một gian hàng nào!</t>
+          <t>Giờ thì thử nâng cấp một gian hàng nào!</t>
         </is>
       </c>
     </row>
@@ -4673,7 +4673,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Bây giờ, hãy thử nâng cấp một quầy hàng nào!</t>
+          <t>Giờ thì thử nâng cấp một gian hàng nào!</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4738,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Bạn có thể kiểm tra Mục Tiêu và phần thưởng trong Dedication Ánh Trăng.</t>
+          <t>Cậu có thể kiểm tra Mục tiêu và phần thưởng trong Moonlit Offerings.</t>
         </is>
       </c>
     </row>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>{0} Bạn có thể kiểm tra Mục Tiêu và phần thưởng trong Moonlit Offerings.</t>
+          <t>{0} Cậu có thể kiểm tra Mục tiêu và phần thưởng trong Moonlit Offerings.</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Bạn có thể kiểm tra Mục Tiêu và phần thưởng trong Dedication Ánh Trăng.</t>
+          <t>Cậu có thể kiểm tra Mục tiêu và phần thưởng trong Moonlit Offerings.</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4933,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ Tale of Moontree Lodge để nhận Astrites!</t>
+          <t>Hoàn thành chuỗi nhiệm vụ Truyện Nhà Trọ Mặt Trăng để nhận Astrites!</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ Tale of Moontree Lodge để nhận Astrites!</t>
+          <t>Hoàn thành chuỗi nhiệm vụ Truyện Nhà Trọ Mặt Trăng để nhận Astrites!</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiệm vụ Tale of Moontree Lodge để nhận Astrites!</t>
+          <t>Hoàn thành chuỗi nhiệm vụ Truyện Nhà Trọ Mặt Trăng để nhận Astrites!</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Hoàn Thành Mục Tiêu để nhận Palace Lantern.</t>
+          <t>Hoàn thành Mục Tiêu để nhận Đèn Lồng Cung Điện</t>
         </is>
       </c>
     </row>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Hoàn Thành Mục Tiêu để nhận Palace Lantern.</t>
+          <t>Hoàn thành Mục Tiêu để nhận Đèn Lồng Cung Điện</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Hoàn Thành Mục Tiêu để nhận Palace Lantern.</t>
+          <t>Hoàn thành Mục Tiêu để nhận Đèn Lồng Cung Điện</t>
         </is>
       </c>
     </row>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Bạn có thể sử dụng Palace Lantern để đổi lấy phần thưởng tại đây.</t>
+          <t>Cậu có thể dùng Đèn Lồng Hoàng Cung để đổi lấy phần thưởng tại đây.</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Bạn có thể sử dụng Palace Lantern để đổi lấy phần thưởng tại đây.</t>
+          <t>Cậu có thể dùng Đèn Lồng Hoàng Cung để đổi lấy phần thưởng tại đây.</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Bạn có thể sử dụng Palace Lantern để đổi lấy phần thưởng tại đây.</t>
+          <t>Cậu có thể dùng Đèn Lồng Hoàng Cung để đổi lấy phần thưởng tại đây.</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Tương tác với Companions để tăng chỉ số của họ.</t>
+          <t>Tương tác với Đồng Hành để tăng chỉ số của họ.</t>
         </is>
       </c>
     </row>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>{0} Tương tác với Companions để tăng chỉ số của họ.</t>
+          <t>{0} hãy tương tác với Đồng Hành để tăng chỉ số cho họ.</t>
         </is>
       </c>
     </row>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Tương tác với Companions để tăng chỉ số của họ.</t>
+          <t>Tương tác với Đồng Hành để tăng chỉ số của họ.</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Chọn Zhezhi để cùng trải qua khoảnh khắc đáng nhớ.</t>
+          <t>Chọn Triết Tri để cùng trải qua khoảnh khắc đáng nhớ</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Chọn Zhezhi để cùng trải qua khoảnh khắc đáng nhớ.</t>
+          <t>Chọn Triết Tri để cùng trải qua khoảnh khắc đáng nhớ</t>
         </is>
       </c>
     </row>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Chọn Zhezhi để cùng trải qua khoảnh khắc đáng nhớ.</t>
+          <t>Chọn Triết Tri để cùng trải qua khoảnh khắc đáng nhớ</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Chọn Tương Ly Yao để cùng trải qua khoảnh khắc đáng nhớ.</t>
+          <t>Chọn Tương Lệ Dao để cùng trải qua khoảnh khắc đáng nhớ</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Chọn Tương Ly Yao để cùng trải qua khoảnh khắc đáng nhớ.</t>
+          <t>Chọn Tương Lệ Dao để cùng trải qua khoảnh khắc đáng nhớ</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Chọn Tương Ly Yao để cùng trải qua khoảnh khắc đáng nhớ.</t>
+          <t>Chọn Tương Lệ Dao để cùng trải qua khoảnh khắc đáng nhớ</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Nhấn {0} để chuyển đổi loại cổng</t>
+          <t>Nhấn {0} để chuyển loại cổng dịch chuyển</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Nhấn {0} để chuyển đổi loại cổng</t>
+          <t>Nhấn {0} để chuyển loại cổng dịch chuyển</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Xem chi tiết buff</t>
+          <t>Xem chi tiết hiệu ứng tăng cường</t>
         </is>
       </c>
     </row>
@@ -6363,7 +6363,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>{0}+{1} to view buff details</t>
+          <t>Nhấn {0}+{1} để xem chi tiết hiệu ứng tăng cường</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Xem chi tiết buff</t>
+          <t>Xem chi tiết hiệu ứng tăng cường</t>
         </is>
       </c>
     </row>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Xem các buff đã nhận</t>
+          <t>Xem các hiệu ứng tăng cường đã nhận</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>{0} to view buffs obtained</t>
+          <t>Nhấn {0} để xem các hiệu ứng tăng cường đã nhận</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Xem các buff đã nhận</t>
+          <t>Xem các hiệu ứng tăng cường đã nhận</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Khi nhận được một số lượng buff nhất định, bạn có thể mở khóa High-Capacity Variable.</t>
+          <t>Khi đạt đủ số lượng buff nhất định, cậu có thể mở khóa High-Capacity Variables.</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Khi nhận được một số lượng buff nhất định, bạn có thể mở khóa High-Capacity Variable.</t>
+          <t>Khi đạt đủ số lượng buff nhất định, cậu có thể mở khóa High-Capacity Variables.</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Khi nhận được một số lượng buff nhất định, bạn có thể mở khóa High-Capacity Variable.</t>
+          <t>Khi đạt đủ số lượng buff nhất định, cậu có thể mở khóa High-Capacity Variables.</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Xem kỹ năng Echo Hỗ Trợ</t>
+          <t>Xem kỹ năng Hỗ Trợ Echo</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Xem kỹ năng Echo Hỗ Trợ</t>
+          <t>Xem kỹ năng Hỗ Trợ Echo</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Xem kỹ năng Echo Hỗ Trợ</t>
+          <t>Xem kỹ năng Hỗ Trợ Echo</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Press {0} to enter Chế Độ Co-op</t>
+          <t>Nhấn {0} để vào Chế Độ Hợp Tác</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Giữ {0} để điều khiển KU-Key và xóa tham nhũng.</t>
+          <t>Giữ {0} để điều khiển KU-Key và thanh tẩy sự ô uế.</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Giữ {0} để điều khiển KU-Key và xóa tham nhũng.</t>
+          <t>Giữ {0} để điều khiển KU-Key và thanh tẩy sự ô uế.</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Giữ để điều khiển KU-Key và xóa tham nhũng.</t>
+          <t>Giữ để điều khiển KU-Key và xóa bỏ sự tha hóa.</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>{0} Nhấn nút tương tác để dùng &lt;color=#8c7e51&gt;Finishing Attack&lt;/color&gt; khi kẻ địch bị Bất Động.</t>
+          <t>Nhấn nút tương tác để sử dụng &lt;color=#8c7e51&gt;Đòn Kết Liễu&lt;/color&gt; khi kẻ địch bị Bất Động.</t>
         </is>
       </c>
     </row>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Nhấn nút Tương tác để dùng &lt;color=#8c7e51&gt;Finishing Attack&lt;/color&gt; khi Crownless bị bất động</t>
+          <t>Khi Crownless bị Hóa Đá, nhấn nút Tương Tác để sử dụng &lt;color=#8c7e51&gt;Đòn Kết Liễu&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8053,7 +8053,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Chạm vào đây để dùng &lt;color=#8c7e51&gt;Basic Attack&lt;/color&gt;</t>
+          <t>Chạm vào đây để sử dụng &lt;color=#8c7e51&gt;Basic Attack&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Giữ để dùng &lt;color=#8c7e51&gt;Heavy Attack&lt;/color&gt;</t>
+          <t>Giữ để sử dụng &lt;color=#8c7e51&gt;Đòn Tấn Công Mạnh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Chạm để &lt;color=#8c7e51&gt;hấp thụ Echo&lt;/color&gt;</t>
+          <t>Nhấn để &lt;color=#8c7e51&gt;hấp thụ Echo&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8378,7 +8378,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Chạm &lt;color=#8c7e51&gt;Tham gia&lt;/color&gt;</t>
+          <t>Chạm &lt;color=#8c7e51&gt;Tham Gia&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Chạm &lt;color=#8c7e51&gt;Triệu Tập&lt;/color&gt; để có những đồng đội đáng tin cậy và vũ khí tiện dụng</t>
+          <t>Chạm &lt;color=#8c7e51&gt;Tập Hợp&lt;/color&gt; để có đồng đội đáng tin và vũ khí tiện dụng</t>
         </is>
       </c>
     </row>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Chạm "Triển khai"</t>
+          <t>Chạm "Triển Khai"</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Chạm "Thử thách đơn"</t>
+          <t>Chạm "Thử Thách Đơn"</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Chạm "Kích hoạt"</t>
+          <t>Chạm "Kích Hoạt"</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Chạm vào đây để &lt;color=#8c7e51&gt;ngắm&lt;/color&gt;</t>
+          <t>Nhấn vào đây để &lt;color=#8c7e51&gt;ngắm&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8768,7 +8768,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Nhấn &lt;color=#8c7e51&gt;Replace&lt;/color&gt;</t>
+          <t>Chạm &lt;color=#8c7e51&gt;Thay Thế&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8833,7 +8833,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Nhấn ngay để kích hoạt &lt;color=#8c7e51&gt;Dodge&lt;/color&gt;</t>
+          <t>Chạm ngay để kích hoạt &lt;color=#8c7e51&gt;Né Tránh&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8898,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Theo dõi hoặc hủy theo dõi Nhiệm vụ</t>
+          <t>Theo dõi hoặc hủy theo dõi Nhiệm Vụ</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Theo dõi hoặc hủy theo dõi Nhiệm vụ</t>
+          <t>Theo dõi hoặc hủy theo dõi Nhiệm Vụ</t>
         </is>
       </c>
     </row>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Chạm nút để nhảy qua đoạn đường đứt gãy</t>
+          <t>Nhấn nút để nhảy qua đoạn đường đứt gãy</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Chạm để &lt;color=#8c7e51&gt;Nhảy&lt;/color&gt;</t>
+          <t>Nhấn để &lt;color=#8c7e51&gt;Nhảy&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>{0} Chạm &lt;color=#8c7e51&gt;Nâng cấp&lt;/color&gt;</t>
+          <t>Nhấn &lt;color=#8c7e51&gt;Nâng Cấp&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Giữ &lt;color=#8c7e51&gt;needle&lt;/color&gt; để di chuyển</t>
+          <t>Giữ &lt;color=#8c7e51&gt;que điều khiển&lt;/color&gt; để di chuyển</t>
         </is>
       </c>
     </row>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Stand cạnh tường và di chuyển &lt;color=#8c7e51&gt;stick&lt;/color&gt; để leo</t>
+          <t>Dựa vào tường và di chuyển &lt;color=#8c7e51&gt;cần điều khiển&lt;/color&gt; để leo lên</t>
         </is>
       </c>
     </row>
@@ -9353,7 +9353,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Đổi Astrites và nhiều phần thưởng khác tại Illusive Cửa hàng</t>
+          <t>Đổi Astrites và nhiều phần thưởng khác tại Cửa Hàng Ảo Ảnh</t>
         </is>
       </c>
     </row>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Đổi Astrites và nhiều phần thưởng khác tại Illusive Cửa hàng</t>
+          <t>Đổi Astrites và nhiều phần thưởng khác tại Cửa Hàng Ảo Ảnh</t>
         </is>
       </c>
     </row>
@@ -9483,7 +9483,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Đổi Astrites và nhiều phần thưởng khác tại Illusive Cửa hàng</t>
+          <t>Đổi Astrites và nhiều phần thưởng khác tại Cửa Hàng Ảo Ảnh</t>
         </is>
       </c>
     </row>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Nhấn {0} để chuyển sang bản đồ khác</t>
+          <t>Nhấn {0} để chuyển sang bản đồ khác.</t>
         </is>
       </c>
     </row>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Chạm để chuyển bản đồ khác</t>
+          <t>Chạm để chuyển sang bản đồ khác</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9743,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Nhấn để chọn Kỹ Năng Buff</t>
+          <t>Nhấn để chọn Kỹ Năng Hỗ Trợ</t>
         </is>
       </c>
     </row>
@@ -9808,7 +9808,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Nhấn {0} để chọn Kỹ năng Hỗ trợ khác</t>
+          <t>Nhấn {0} để chọn một Kỹ Năng Tăng Cường khác.</t>
         </is>
       </c>
     </row>
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Chạm để chọn Kỹ năng Buff khác</t>
+          <t>Chạm để chọn Kỹ năng Tăng cường khác</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Nhấn để chọn Kỹ năng Tăng cường cho giai đoạn này</t>
+          <t>Nhấn để chọn Kỹ Năng Hỗ Trợ cho giai đoạn này</t>
         </is>
       </c>
     </row>
@@ -10003,7 +10003,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Nhấn {0} để chọn Kỹ Năng Buff cho giai đoạn này</t>
+          <t>Nhấn {0} để chọn Kỹ Năng Tăng Cường cho giai đoạn này.</t>
         </is>
       </c>
     </row>
@@ -10133,7 +10133,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Nhấn để chọn Main Resonator</t>
+          <t>Nhấn để chọn Resonator chính</t>
         </is>
       </c>
     </row>
@@ -10198,7 +10198,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Nhấn {0} để chọn Resonator Mian</t>
+          <t>Nhấn {0} để chọn Resonator Mian.</t>
         </is>
       </c>
     </row>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Chạm để chọn Main Resonator</t>
+          <t>Chạm để chọn Resonator chính</t>
         </is>
       </c>
     </row>
@@ -10328,7 +10328,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Nhấn để kiểm tra Resonator Enhancements đang kích hoạt</t>
+          <t>Nhấn để kiểm tra các Tăng Cường Resonator đang hoạt động</t>
         </is>
       </c>
     </row>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Nhấn {0} để kiểm tra Resonator Enhancements đang hoạt động</t>
+          <t>Nhấn {0} để kiểm tra các Tăng Cường Resonator đang hoạt động</t>
         </is>
       </c>
     </row>
@@ -10458,7 +10458,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Chạm để kiểm tra Resonator Enhancements đang kích hoạt</t>
+          <t>Chạm để kiểm tra các Tăng Cường Resonator đang kích hoạt</t>
         </is>
       </c>
     </row>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Nhấn để đọc thông tin sự kiện thường trực</t>
+          <t>Nhấn để xem thông tin sự kiện thường trực</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Nhấn {0} để xem thông tin sự kiện thường trực</t>
+          <t>Nhấn {0} để đọc thông tin sự kiện thường trực</t>
         </is>
       </c>
     </row>
@@ -10718,7 +10718,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Nhấn vào đây để bước vào giấc mơ của Resonators khác</t>
+          <t>Nhấn vào đây để đắm chìm trong giấc mơ của các Resonator khác</t>
         </is>
       </c>
     </row>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Nhấn {0} để đắm chìm vào giấc mơ của Resonators khác nhau</t>
+          <t>Nhấn {0} để đắm chìm vào giấc mơ của các Resonator khác</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10848,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Chạm để bước vào giấc mơ của Resonators khác</t>
+          <t>Chạm để bước vào giấc mơ của các Resonator khác</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Gây DMG hoặc Dodge để nhận Sync Energy</t>
+          <t>Gây sát thương hoặc Né để tích Lượng Đồng Bộ</t>
         </is>
       </c>
     </row>
@@ -10978,7 +10978,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Gây DMG hoặc Dodge để nhận Sync Energy</t>
+          <t>Gây sát thương hoặc Né để tích Lượng Đồng Bộ</t>
         </is>
       </c>
     </row>
@@ -11043,7 +11043,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Gây DMG hoặc Dodge để nhận Sync Energy</t>
+          <t>Gây sát thương hoặc Né để tích Lượng Đồng Bộ</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Khi Năng lượng Đồng bộ đầy, chuẩn bị kích hoạt Liên kết Giấc mơ</t>
+          <t>Khi Năng Lượng Đồng Bộ đạt tối đa, chuẩn bị kích hoạt Liên Kết Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -11173,7 +11173,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Khi Năng lượng Đồng bộ đầy, chuẩn bị kích hoạt Liên kết Giấc mơ</t>
+          <t>Khi Năng Lượng Đồng Bộ đạt tối đa, chuẩn bị kích hoạt Liên Kết Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -11238,7 +11238,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Khi Năng lượng Đồng bộ đầy, chuẩn bị kích hoạt Liên kết Giấc mơ</t>
+          <t>Khi Năng Lượng Đồng Bộ đạt tối đa, chuẩn bị kích hoạt Liên Kết Giấc Mơ.</t>
         </is>
       </c>
     </row>
@@ -11303,7 +11303,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Nhấn {0} để sử dụng Resonance Liberation và kích hoạt Dream Link</t>
+          <t>Nhấn {0} để tung Resonance Liberation và kích hoạt Liên Kết Giấc Mơ</t>
         </is>
       </c>
     </row>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Dùng Resonance Liberation để kích hoạt Dream Link</t>
+          <t>Kích hoạt Resonance Liberation để kích hoạt Liên Kết Giấc Mơ</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Dùng Resonance Liberation của Resonator Hỗ Trợ</t>
+          <t>Kích hoạt Resonance Liberation của Resonator Hỗ Trợ</t>
         </is>
       </c>
     </row>
@@ -11498,7 +11498,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Dùng Resonance Liberation của Resonator Hỗ Trợ</t>
+          <t>Kích hoạt Resonance Liberation của Resonator Hỗ Trợ</t>
         </is>
       </c>
     </row>
@@ -11563,7 +11563,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Dùng Resonance Liberation của Resonator Hỗ Trợ</t>
+          <t>Kích hoạt Resonance Liberation của Resonator Hỗ Trợ</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Bấm vào các ô để đổi Nhật Ký Phiêu Lưu lấy Gói Phiêu Lưu</t>
+          <t>Nhấn vào các ô để đổi Nhật Ký Phiêu Lưu lấy Gói Phiêu Lưu</t>
         </is>
       </c>
     </row>
@@ -11693,7 +11693,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Trigger ô để đổi Nhật Ký Phiêu Lưu lấy Gói Phiêu Lưu</t>
+          <t>Kích hoạt ô để đổi Gói Phiêu Lưu bằng Nhật Ký Phiêu Lưu</t>
         </is>
       </c>
     </row>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Chọn Resonators hỗ trợ sẽ tự động chiến đấu cùng bạn</t>
+          <t>Chọn Resonator sẽ tự động chiến đấu bên cạnh bạn</t>
         </is>
       </c>
     </row>
@@ -11888,7 +11888,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Chọn Resonators hỗ trợ sẽ tự động chiến đấu cùng bạn</t>
+          <t>Chọn Resonator sẽ tự động chiến đấu bên cạnh bạn</t>
         </is>
       </c>
     </row>
@@ -11953,7 +11953,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Chọn Resonators hỗ trợ sẽ tự động chiến đấu cùng bạn</t>
+          <t>Chọn Resonator sẽ tự động chiến đấu bên cạnh bạn</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Trong khi khám phá Somnoire, bạn có thể gặp một con mèo trắng kỳ lạ mang đến những cải tiến đáng kể cho Resonators của bạn.</t>
+          <t>Trong lúc khám phá Somnoire, bạn có thể gặp một con mèo trắng kỳ lạ, nó có thể mang lại những cải tiến đáng kể cho Resonator của bạn.</t>
         </is>
       </c>
     </row>
@@ -12083,7 +12083,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Explore những giấc mơ khác nhau để giúp chú mèo trắng lấy lại quyền kiểm soát Somnoire.</t>
+          <t>Khám phá những giấc mơ khác nhau để giúp mèo trắng lấy lại quyền kiểm soát Somnoire</t>
         </is>
       </c>
     </row>
@@ -12148,7 +12148,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Kích hoạt Intro Skill sẽ phục hồi Forte Gauge. Các đòn tấn công tiêu hao Forte Gauge để tăng DMG hoặc phục hồi Resonance Energy.</t>
+          <t>Kích hoạt Kỹ Năng Khởi Động sẽ hồi phục Thanh Forte. Các đòn tấn công sẽ tiêu hao Thanh Forte để tăng Sát Thương hoặc hồi phục Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -12213,7 +12213,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Kích hoạt Intro Skill sẽ phục hồi Forte Gauge. Các đòn tấn công tiêu hao Forte Gauge để tăng DMG hoặc phục hồi Resonance Energy.</t>
+          <t>Kích hoạt Kỹ Năng Khởi Động sẽ hồi phục Thanh Forte. Các đòn tấn công sẽ tiêu hao Thanh Forte để tăng Sát Thương hoặc hồi phục Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Kích hoạt Intro Skill sẽ phục hồi Forte Gauge. Các đòn tấn công tiêu hao Forte Gauge để tăng DMG hoặc phục hồi Resonance Energy.</t>
+          <t>Kích hoạt Kỹ Năng Khởi Động sẽ hồi phục Thanh Forte. Các đòn tấn công sẽ tiêu hao Thanh Forte để tăng Sát Thương hoặc hồi phục Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -12538,7 +12538,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Resonance Skill được thay thế bằng Ephemeral của Forte Circuit khi Concerto Energy đầy. Sử dụng kỹ năng này liên tục sẽ phục hồi Forte Gauge.</t>
+          <t>Kỹ năng Cộng Hưởng được thay thế bằng Ephemeral của Forte Circuit khi Concerto Energy đầy. Sử dụng kỹ năng liên tục sẽ hồi phục Thanh Forte.</t>
         </is>
       </c>
     </row>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Resonance Skill được thay thế bằng Ephemeral của Forte Circuit khi Concerto Energy đầy. Sử dụng kỹ năng này liên tục sẽ phục hồi Forte Gauge.</t>
+          <t>Kỹ năng Cộng Hưởng được thay thế bằng Ephemeral của Forte Circuit khi Concerto Energy đầy. Sử dụng kỹ năng liên tục sẽ hồi phục Thanh Forte.</t>
         </is>
       </c>
     </row>
@@ -12668,7 +12668,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Resonance Skill được thay thế bằng Ephemeral của Forte Circuit khi Concerto Energy đầy. Sử dụng kỹ năng này liên tục sẽ phục hồi Forte Gauge.</t>
+          <t>Kỹ năng Cộng Hưởng được thay thế bằng Ephemeral của Forte Circuit khi Concerto Energy đầy. Sử dụng kỹ năng liên tục sẽ hồi phục Thanh Forte.</t>
         </is>
       </c>
     </row>
@@ -12733,7 +12733,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Dùng kỹ năng sẽ phục hồi Forte Gauge.</t>
+          <t>Kích hoạt kỹ năng sẽ hồi phục Thanh Forte.</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Dùng kỹ năng sẽ phục hồi Forte Gauge.</t>
+          <t>Kích hoạt kỹ năng sẽ hồi phục Thanh Forte.</t>
         </is>
       </c>
     </row>
@@ -12863,7 +12863,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Dùng kỹ năng sẽ phục hồi Forte Gauge.</t>
+          <t>Kích hoạt kỹ năng sẽ hồi phục Thanh Forte.</t>
         </is>
       </c>
     </row>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Sử dụng Heavy Attack khi Forte Gauge đầy sẽ thực hiện Heavy Attack: Imminent Oblivion.</t>
+          <t>Khi Thanh Forte đầy, sử dụng Đòn Tấn Công Mạnh sẽ thực hiện Đòn Tấn Công Mạnh: Hủy Diệt Sắp Đến.</t>
         </is>
       </c>
     </row>
@@ -12993,7 +12993,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Thực hiện Basic Attack 2 để phục hồi 3 &lt;color=#1891e7ff&gt;Tinh Thể Dẻo&lt;/color&gt; (tối đa 6 Tinh Thể).</t>
+          <t>Basic Attack 2 lần để hồi 3 &lt;color=#1891e7ff&gt;Tinh Thể Dẻo&lt;/color&gt; (tối đa 6 Tinh Thể).</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13058,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Ngay sau khi dùng Heavy Attack: Imminent Oblivion, nếu dùng lại Heavy Attack khi Forte Gauge đã đầy sẽ thực hiện Heavy Attack: Containment Tactics.</t>
+          <t>Ngay sau khi tung chiêu Heavy Attack: Imminent Oblivion, using Heavy Attack again with full Forte Gauge performs Heavy Attack: Containment Tactics.</t>
         </is>
       </c>
     </row>
@@ -13123,7 +13123,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Trong Beyond Imagination, dùng Basic Attack để tiêu hao 100 Imagination và tung đòn Chain Plunging Attack.</t>
+          <t>Trong trạng thái Vượt Qua Tưởng Tượng, sử dụng Đòn Basic Attack để tiêu hao 100 Điểm Tưởng Tượng và tung ra Đòn Lao Xuống Xích.</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Giữ Basic Attack để sạc và phục hồi Forte Gauge.</t>
+          <t>Giữ Basic Attack để tích năng và phục hồi Thanh Forte.</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Nếu Imagination còn lại trên 100 sau khi sử dụng Plunging Attack được tăng cường, Roccia sẽ bay lên không trung và kích hoạt Beyond Imagination một lần nữa.</t>
+          <t>Nếu Lượng Tưởng Tượng còn lại trên 100 sau khi sử dụng Kỹ Năng Đâm Xuống được tăng cường, Roccia sẽ bay lên không trung và kích hoạt Vượt Giới Tưởng Tượng một lần nữa.</t>
         </is>
       </c>
     </row>
@@ -13318,7 +13318,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Khi Concerto Energy đầy, Roccia thay thế Công cụ của Resonator sắp xuất hiện bằng Magic Box để kéo kẻ địch về phía nó.</t>
+          <t>Khi Concerto Energy đạt tối đa, Roccia sẽ thay thế Tiện Ích của Resonator đang đến bằng Hộp Ma Thuật, kéo kẻ địch về phía nó.</t>
         </is>
       </c>
     </row>
@@ -13383,7 +13383,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Dùng Hộp Ma thuật Roccia để kéo kẻ địch lại gần.</t>
+          <t>Dùng Hộp Ma Thuật của Roccia để kéo kẻ địch vào.</t>
         </is>
       </c>
     </row>
@@ -13513,7 +13513,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Khi Forte Gauge đầy, Carlotta bước vào Final Bow, làm tăng Hệ Số DMG Resonance Liberation.</t>
+          <t>Khi Thanh Forte đầy, Carlotta bước vào trạng thái Cú Đánh Cuối, tăng Hệ Số Sát Thương Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -13578,7 +13578,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Khi Concerto Energy đầy đủ, Brant có thể được đưa vào trận và dùng móc câu tấn công mục tiêu.</t>
+          <t>Khi Năng Lượng Giao Hưởng đạt tối đa, có thể đổi Brant vào chiến trường, hắn sẽ vung móc câu tấn công mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -13643,7 +13643,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Khi Concerto Energy đầy&lt;/color&gt;, có thể đổi sang Phoebe và gây Spectro DMG lên mục tiêu gần đó.</t>
+          <t>Khi &lt;color=Highlight&gt;Concerto Energy&lt;/color&gt; đầy đủ, có thể triệu hồi Phoebe vào trận và gây Sát Thương Spectro lên các mục tiêu xung quanh.</t>
         </is>
       </c>
     </row>
@@ -13708,7 +13708,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Khi Bravo được phục hồi hoàn toàn, thay thế Anchor Aweigh bằng Returned from Ashes. Tiêu hao toàn bộ Bravo để thực hiện Returned from Ashes, gây Fusion DMG và nhận khiên.</t>
+          <t>Khi Bravo được hồi phục đầy đủ, thay thế Anchor Aweigh bằng Returned from Ashes. Tiêu hao toàn bộ Bravo để thực hiện Returned from Ashes, gây DMG Fusion và nhận khiên.</t>
         </is>
       </c>
     </row>
@@ -13773,7 +13773,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Sau khi dùng Intro Skill, sử dụng Resonance Liberation.</t>
+          <t>Sau khi thực hiện Kỹ Năng Khởi Động, hãy tung Kỹ Năng Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -13838,7 +13838,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Sau khi dùng Resonance Skill, thực hiện Mid-air Attack trong lúc hạ cánh.</t>
+          <t>Sau khi sử dụng Resonance Skill, thực hiện Tấn Công Giữa Không trong lúc hạ cánh.</t>
         </is>
       </c>
     </row>
@@ -13903,7 +13903,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Khi Prayer đầy, giữ **Normal Attack** để thi triển &lt;color=Highlight&gt;Absolution Litany&lt;/color&gt; và vào trạng thái Absolution.</t>
+          <t>Khi Prayer đạt tối đa, giữ Normal Attack để thi triển &lt;color=Highlight&gt;Absolution Litany&lt;/color&gt; và bước vào trạng thái Absolution.</t>
         </is>
       </c>
     </row>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Khi Prayer đầy, giữ Resonance Skill để thi triển &lt;color=Highlight&gt;Utter Confession&lt;/color&gt; và进入 Confession status.</t>
+          <t>Khi Prayer đạt tối đa, giữ Resonance Skill để thi triển &lt;color=Highlight&gt;Utter Confession&lt;/color&gt; và bước vào trạng thái Confession.</t>
         </is>
       </c>
     </row>
@@ -14033,7 +14033,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Giai đoạn Basic Attack 3&lt;/color&gt; phục hồi 1 điểm Trance khi trúng mục tiêu.</t>
+          <t>&lt;color=Highlight&gt;Basic Attack Cấp 3&lt;/color&gt; hồi phục 1 điểm Trance khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Giai đoạn Basic Attack 3&lt;/color&gt; phục hồi 1 điểm Trance khi trúng mục tiêu.</t>
+          <t>&lt;color=Highlight&gt;Basic Attack Cấp 3&lt;/color&gt; hồi phục 1 điểm Trance khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Giai đoạn Basic Attack 3&lt;/color&gt; phục hồi 1 điểm Trance khi trúng mục tiêu.</t>
+          <t>&lt;color=Highlight&gt;Basic Attack Cấp 3&lt;/color&gt; hồi phục 1 điểm Trance khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -14228,7 +14228,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Sử dụng kỹ năng sẽ phục hồi 1 điểm Trance.</t>
+          <t>Kích hoạt kỹ năng sẽ hồi phục 1 điểm Trance.</t>
         </is>
       </c>
     </row>
@@ -14293,7 +14293,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Sử dụng kỹ năng sẽ phục hồi 1 điểm Trance.</t>
+          <t>Kích hoạt kỹ năng sẽ hồi phục 1 điểm Trance.</t>
         </is>
       </c>
     </row>
@@ -14358,7 +14358,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Sử dụng kỹ năng sẽ phục hồi 1 điểm Trance.</t>
+          <t>Kích hoạt kỹ năng sẽ hồi phục 1 điểm Trance.</t>
         </is>
       </c>
     </row>
@@ -14423,7 +14423,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Basic Attack được tăng cường tiêu hao Trance để phục hồi Shiver khi trúng mục tiêu.</t>
+          <t>Basic Attack Nâng Cao tiêu hao Trance để hồi phục Shiver khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -14488,7 +14488,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Basic Attack được tăng cường tiêu hao Trance để phục hồi Shiver khi trúng mục tiêu.</t>
+          <t>Basic Attack Nâng Cao tiêu hao Trance để hồi phục Shiver khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -14553,7 +14553,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Basic Attack được tăng cường tiêu hao Trance để phục hồi Shiver khi trúng mục tiêu.</t>
+          <t>Basic Attack Nâng Cao tiêu hao Trance để hồi phục Shiver khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -14618,7 +14618,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Mid-air Attack Nâng Cao tiêu hao Trance để phục hồi Shiver khi trúng mục tiêu.</t>
+          <t>Đòn Tấn Công Giữa Không Nâng Cao tiêu hao Trance để hồi phục Shiver khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -14683,7 +14683,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Mid-air Attack Nâng Cao tiêu hao Trance để phục hồi Shiver khi trúng mục tiêu.</t>
+          <t>Đòn Tấn Công Giữa Không Nâng Cao tiêu hao Trance để hồi phục Shiver khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -14748,7 +14748,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Mid-air Attack Nâng Cao tiêu hao Trance để phục hồi Shiver khi trúng mục tiêu.</t>
+          <t>Đòn Tấn Công Giữa Không Nâng Cao tiêu hao Trance để hồi phục Shiver khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -14813,7 +14813,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Resonance Skill &lt;color=Highlight&gt;Perception Drain&lt;/color&gt; sẵn sàng khi có 3 điểm Shiver.</t>
+          <t>Kỹ năng Cộng hưởng &lt;color=Highlight&gt;Hút Nhận Thức&lt;/color&gt; đã sẵn sàng với 3 điểm Run Rẩy.</t>
         </is>
       </c>
     </row>
@@ -14878,7 +14878,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Resonance Skill &lt;color=Highlight&gt;Perception Drain&lt;/color&gt; sẵn sàng khi có 3 điểm Shiver.</t>
+          <t>Kỹ năng Cộng hưởng &lt;color=Highlight&gt;Hút Nhận Thức&lt;/color&gt; đã sẵn sàng với 3 điểm Run Rẩy.</t>
         </is>
       </c>
     </row>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Resonance Skill &lt;color=Highlight&gt;Perception Drain&lt;/color&gt; sẵn sàng khi có 3 điểm Shiver.</t>
+          <t>Kỹ năng Cộng hưởng &lt;color=Highlight&gt;Hút Nhận Thức&lt;/color&gt; đã sẵn sàng với 3 điểm Run Rẩy.</t>
         </is>
       </c>
     </row>
@@ -15008,7 +15008,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Sử dụng Resonance Liberation sẽ phục hồi 3 điểm Trance.</t>
+          <t>Kích hoạt Resonance Liberation hồi phục 3 điểm Trance.</t>
         </is>
       </c>
     </row>
@@ -15073,7 +15073,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Sử dụng Resonance Liberation sẽ phục hồi 3 điểm Trance.</t>
+          <t>Kích hoạt Resonance Liberation hồi phục 3 điểm Trance.</t>
         </is>
       </c>
     </row>
@@ -15138,7 +15138,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Sử dụng Resonance Liberation sẽ phục hồi 3 điểm Trance.</t>
+          <t>Kích hoạt Resonance Liberation hồi phục 3 điểm Trance.</t>
         </is>
       </c>
     </row>
@@ -15203,7 +15203,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=Highlight&gt;Mirage&lt;/color&gt;, dùng Nhảy để thực hiện Mid-air Attack được tăng cường.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Huyễn Ảnh&lt;/color&gt;, sử dụng Nhảy để tung đòn Tấn Công Giữa Không trung được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=Highlight&gt;Mirage&lt;/color&gt;, dùng Nhảy để thực hiện Mid-air Attack được tăng cường.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Huyễn Ảnh&lt;/color&gt;, sử dụng Nhảy để tung đòn Tấn Công Giữa Không trung được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái &lt;color=Highlight&gt;Mirage&lt;/color&gt;, dùng Nhảy để thực hiện Mid-air Attack được tăng cường.</t>
+          <t>Khi ở &lt;color=Highlight&gt;Huyễn Ảnh&lt;/color&gt;, sử dụng Nhảy để tung đòn Tấn Công Giữa Không trung được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Vào &lt;color=Highlight&gt;Mirage&lt;/color&gt;.</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Ảo Ảnh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15463,7 +15463,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Vào &lt;color=Highlight&gt;Mirage&lt;/color&gt;.</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Ảo Ảnh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Vào &lt;color=Highlight&gt;Mirage&lt;/color&gt;.</t>
+          <t>Kích hoạt &lt;color=Highlight&gt;Ảo Ảnh&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15593,7 +15593,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; được thay thế bằng &lt;color=Highlight&gt;Enhanced Resonance Skill&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; được thay thế bằng &lt;color=Highlight&gt;Resonance Skill Nâng Cấp&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; được thay thế bằng &lt;color=Highlight&gt;Enhanced Resonance Skill&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; được thay thế bằng &lt;color=Highlight&gt;Resonance Skill Nâng Cấp&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15723,7 +15723,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; được thay thế bằng &lt;color=Highlight&gt;Enhanced Resonance Skill&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; được thay thế bằng &lt;color=Highlight&gt;Resonance Skill Nâng Cấp&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Sunburst&lt;/color&gt;: Khuếch đại trực tiếp DMG &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt; do Zani gây ra.</t>
+          <t>&lt;color=Highlight&gt;Vụ Nổ Mặt Trời&lt;/color&gt;: Khuếch đại &lt;color=Highlight&gt;Sát Thương Spectro Frazzle&lt;/color&gt; trực tiếp do Zani gây ra.</t>
         </is>
       </c>
     </row>
@@ -15853,7 +15853,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Sunburst&lt;/color&gt;: Khuếch đại trực tiếp DMG &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt; do Zani gây ra.</t>
+          <t>&lt;color=Highlight&gt;Vụ Nổ Mặt Trời&lt;/color&gt;: Khuếch đại &lt;color=Highlight&gt;Sát Thương Spectro Frazzle&lt;/color&gt; trực tiếp do Zani gây ra.</t>
         </is>
       </c>
     </row>
@@ -15918,7 +15918,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Sunburst&lt;/color&gt;: Khuếch đại trực tiếp DMG &lt;color=Highlight&gt;Spectro Frazzle&lt;/color&gt; do Zani gây ra.</t>
+          <t>&lt;color=Highlight&gt;Vụ Nổ Mặt Trời&lt;/color&gt;: Khuếch đại &lt;color=Highlight&gt;Sát Thương Spectro Frazzle&lt;/color&gt; trực tiếp do Zani gây ra.</t>
         </is>
       </c>
     </row>
@@ -15983,7 +15983,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Hướng dẫn Giải phóng Cộng hưởng Nâng cao Cartethyia</t>
+          <t>Hướng dẫn Resonance Liberation Nâng Cao của Cartethyia</t>
         </is>
       </c>
     </row>
@@ -16048,7 +16048,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Hướng dẫn Giải phóng Cộng hưởng Nâng cao Cartethyia</t>
+          <t>Hướng dẫn Resonance Liberation Nâng Cao của Cartethyia</t>
         </is>
       </c>
     </row>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Hướng dẫn Giải phóng Cộng hưởng Nâng cao Cartethyia</t>
+          <t>Hướng dẫn Resonance Liberation Nâng Cao của Cartethyia</t>
         </is>
       </c>
     </row>
@@ -16178,7 +16178,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Các Normal Attack của Lupa phục hồi Wolflame.</t>
+          <t>Các đòn tấn công thông thường của Lupa hồi phục Wolflame.</t>
         </is>
       </c>
     </row>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Các Normal Attack của Lupa phục hồi Wolflame.</t>
+          <t>Các đòn tấn công thông thường của Lupa hồi phục Wolflame.</t>
         </is>
       </c>
     </row>
@@ -16308,7 +16308,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Các Normal Attack của Lupa phục hồi Wolflame.</t>
+          <t>Các đòn tấn công thông thường của Lupa hồi phục Wolflame.</t>
         </is>
       </c>
     </row>
@@ -16373,7 +16373,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Khi có 50 điểm Wolflame, &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; của Lupa sẽ được thay thế bằng &lt;color=Highlight&gt;Enhanced Heavy Attack 1&lt;/color&gt;, tiêu hao 50 điểm Wolflame và nhận 1 điểm Wolfaith.</t>
+          <t>Khi có 50 điểm Ngọn Lửa Sói, &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; của Lupa sẽ được thay thế bằng &lt;color=Highlight&gt;Đòn Heavy Attack Cường Hóa 1&lt;/color&gt;, tiêu hao 50 điểm Ngọn Lửa Sói và nhận được 1 điểm Niềm Tin Sói.</t>
         </is>
       </c>
     </row>
@@ -16438,7 +16438,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Khi có 50 điểm Wolflame, &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; của Lupa sẽ được thay thế bằng &lt;color=Highlight&gt;Enhanced Heavy Attack 1&lt;/color&gt;, tiêu hao 50 điểm Wolflame và nhận 1 điểm Wolfaith.</t>
+          <t>Khi có 50 điểm Ngọn Lửa Sói, &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; của Lupa sẽ được thay thế bằng &lt;color=Highlight&gt;Đòn Heavy Attack Cường Hóa 1&lt;/color&gt;, tiêu hao 50 điểm Ngọn Lửa Sói và nhận được 1 điểm Niềm Tin Sói.</t>
         </is>
       </c>
     </row>
@@ -16503,7 +16503,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Khi có 50 điểm Wolflame, &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; của Lupa sẽ được thay thế bằng &lt;color=Highlight&gt;Enhanced Heavy Attack 1&lt;/color&gt;, tiêu hao 50 điểm Wolflame và nhận 1 điểm Wolfaith.</t>
+          <t>Khi có 50 điểm Ngọn Lửa Sói, &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; của Lupa sẽ được thay thế bằng &lt;color=Highlight&gt;Đòn Heavy Attack Cường Hóa 1&lt;/color&gt;, tiêu hao 50 điểm Ngọn Lửa Sói và nhận được 1 điểm Niềm Tin Sói.</t>
         </is>
       </c>
     </row>
@@ -16568,7 +16568,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Với 50 điểm Wolflame và 1 điểm Wolfaith, &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; của Lupa được thay thế bằng &lt;color=Highlight&gt;Enhanced Heavy Attack 2&lt;/color&gt;, tiêu hao 50 điểm Wolflame và nhận 1 điểm Wolfaith.</t>
+          <t>Với 50 điểm Wolflame và 1 điểm Wolfaith, &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; của Lupa sẽ được thay thế bằng &lt;color=Highlight&gt;Đòn Heavy Attack Tăng Cường 2&lt;/color&gt;, tiêu hao 50 điểm Wolflame và nhận 1 điểm Wolfaith.</t>
         </is>
       </c>
     </row>
@@ -16633,7 +16633,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Với 50 điểm Wolflame và 1 điểm Wolfaith, &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; của Lupa được thay thế bằng &lt;color=Highlight&gt;Enhanced Heavy Attack 2&lt;/color&gt;, tiêu hao 50 điểm Wolflame và nhận 1 điểm Wolfaith.</t>
+          <t>Với 50 điểm Wolflame và 1 điểm Wolfaith, &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; của Lupa sẽ được thay thế bằng &lt;color=Highlight&gt;Đòn Heavy Attack Tăng Cường 2&lt;/color&gt;, tiêu hao 50 điểm Wolflame và nhận 1 điểm Wolfaith.</t>
         </is>
       </c>
     </row>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Với 50 điểm Wolflame và 1 điểm Wolfaith, &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; của Lupa được thay thế bằng &lt;color=Highlight&gt;Enhanced Heavy Attack 2&lt;/color&gt;, tiêu hao 50 điểm Wolflame và nhận 1 điểm Wolfaith.</t>
+          <t>Với 50 điểm Wolflame và 1 điểm Wolfaith, &lt;color=Highlight&gt;Đòn Heavy Attack&lt;/color&gt; của Lupa sẽ được thay thế bằng &lt;color=Highlight&gt;Đòn Heavy Attack Tăng Cường 2&lt;/color&gt;, tiêu hao 50 điểm Wolflame và nhận 1 điểm Wolfaith.</t>
         </is>
       </c>
     </row>
@@ -16763,7 +16763,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Với 50 điểm Wolflame, Stage 3 của Mid-air Attack của Lupa sẽ được thay thế bằng &lt;color=Highlight&gt;Enhanced Mid-air Attack&lt;/color&gt;, tiêu hao 50 điểm Wolflame và nhận 1 điểm Wolfaith.</t>
+          <t>Khi có 50 điểm Ngọn Lửa Sói, Giai Đoạn 3 của Đòn Tấn Công Giữa Không của Lupa sẽ được thay thế bằng &lt;color=Highlight&gt;Đòn Tấn Công Giữa Không Cường Hóa&lt;/color&gt;, tiêu hao 50 điểm Ngọn Lửa Sói và nhận được 1 điểm Niềm Tin Sói.</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Với 50 điểm Wolflame, Stage 3 của Mid-air Attack của Lupa sẽ được thay thế bằng &lt;color=Highlight&gt;Enhanced Mid-air Attack&lt;/color&gt;, tiêu hao 50 điểm Wolflame và nhận 1 điểm Wolfaith.</t>
+          <t>Khi có 50 điểm Ngọn Lửa Sói, Giai Đoạn 3 của Đòn Tấn Công Giữa Không của Lupa sẽ được thay thế bằng &lt;color=Highlight&gt;Đòn Tấn Công Giữa Không Cường Hóa&lt;/color&gt;, tiêu hao 50 điểm Ngọn Lửa Sói và nhận được 1 điểm Niềm Tin Sói.</t>
         </is>
       </c>
     </row>
@@ -16893,7 +16893,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Với 50 điểm Wolflame, Stage 3 của Mid-air Attack của Lupa sẽ được thay thế bằng &lt;color=Highlight&gt;Enhanced Mid-air Attack&lt;/color&gt;, tiêu hao 50 điểm Wolflame và nhận 1 điểm Wolfaith.</t>
+          <t>Khi có 50 điểm Ngọn Lửa Sói, Giai Đoạn 3 của Đòn Tấn Công Giữa Không của Lupa sẽ được thay thế bằng &lt;color=Highlight&gt;Đòn Tấn Công Giữa Không Cường Hóa&lt;/color&gt;, tiêu hao 50 điểm Ngọn Lửa Sói và nhận được 1 điểm Niềm Tin Sói.</t>
         </is>
       </c>
     </row>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Với 2 điểm Wolfaith, Resonance Skill được thay thế bằng &lt;color=Highlight&gt;Resonance Skill Finisher&lt;/color&gt;.</t>
+          <t>Với 2 điểm Wolfaith, Resonance Skill sẽ được thay thế bằng &lt;color=Highlight&gt;Resonance Skill Hoàn Thành&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17023,7 +17023,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Với 2 điểm Wolfaith, Resonance Skill được thay thế bằng &lt;color=Highlight&gt;Resonance Skill Finisher&lt;/color&gt;.</t>
+          <t>Với 2 điểm Wolfaith, Resonance Skill sẽ được thay thế bằng &lt;color=Highlight&gt;Resonance Skill Hoàn Thành&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17088,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Với 2 điểm Wolfaith, Resonance Skill được thay thế bằng &lt;color=Highlight&gt;Resonance Skill Finisher&lt;/color&gt;.</t>
+          <t>Với 2 điểm Wolfaith, Resonance Skill sẽ được thay thế bằng &lt;color=Highlight&gt;Resonance Skill Hoàn Thành&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17153,7 +17153,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation sẽ thay thế đòn tấn công tiếp theo bằng Foebreaker, tiêu hao 100 điểm Wolflame để kích hoạt Burning Matchpoint.</t>
+          <t>Kích hoạt Resonance Liberation sẽ thay thế đòn tấn công tiếp theo bằng Foebreaker, tiêu hao 100 Wolflame để kích hoạt Burning Matchpoint.</t>
         </is>
       </c>
     </row>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation sẽ thay thế đòn tấn công tiếp theo bằng Foebreaker, tiêu hao 100 điểm Wolflame để kích hoạt Burning Matchpoint.</t>
+          <t>Kích hoạt Resonance Liberation sẽ thay thế đòn tấn công tiếp theo bằng Foebreaker, tiêu hao 100 Wolflame để kích hoạt Burning Matchpoint.</t>
         </is>
       </c>
     </row>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation sẽ thay thế đòn tấn công tiếp theo bằng Foebreaker, tiêu hao 100 điểm Wolflame để kích hoạt Burning Matchpoint.</t>
+          <t>Kích hoạt Resonance Liberation sẽ thay thế đòn tấn công tiếp theo bằng Foebreaker, tiêu hao 100 Wolflame để kích hoạt Burning Matchpoint.</t>
         </is>
       </c>
     </row>
@@ -17348,7 +17348,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Khi Lupa nhảy lên khỏi mặt đất ở cuối &lt;color=Highlight&gt;Basic Attack 3&lt;/color&gt;, dùng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Mid-air Attack 1&lt;/color&gt;.</t>
+          <t>Khi Lupa nhảy lên khỏi mặt đất ở cuối &lt;color=Highlight&gt;Đòn Basic Attack 3&lt;/color&gt;, hãy dùng &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; để tung ra &lt;color=Highlight&gt;Đòn Mid-air Attack 1&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17413,7 +17413,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Khi Lupa nhảy lên khỏi mặt đất ở cuối &lt;color=Highlight&gt;Basic Attack 3&lt;/color&gt;, dùng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Mid-air Attack 1&lt;/color&gt;.</t>
+          <t>Khi Lupa nhảy lên khỏi mặt đất ở cuối &lt;color=Highlight&gt;Đòn Basic Attack 3&lt;/color&gt;, hãy dùng &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; để tung ra &lt;color=Highlight&gt;Đòn Mid-air Attack 1&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17478,7 +17478,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Khi Lupa nhảy lên khỏi mặt đất ở cuối &lt;color=Highlight&gt;Basic Attack 3&lt;/color&gt;, dùng &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Mid-air Attack 1&lt;/color&gt;.</t>
+          <t>Khi Lupa nhảy lên khỏi mặt đất ở cuối &lt;color=Highlight&gt;Đòn Basic Attack 3&lt;/color&gt;, hãy dùng &lt;color=Highlight&gt;Đòn Basic Attack&lt;/color&gt; để tung ra &lt;color=Highlight&gt;Đòn Mid-air Attack 1&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Nhấn {0} để mời đồng hành cưỡi cùng</t>
+          <t>Nhấn {0} để mời một người bạn đồng hành lên xe</t>
         </is>
       </c>
     </row>
@@ -17608,7 +17608,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Invite bạn đồng hành cùng cưỡi</t>
+          <t>Mời bạn đồng hành đi cùng</t>
         </is>
       </c>
     </row>
@@ -17673,7 +17673,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Bây giờ bạn có thể thay đổi Ngoại Hình của Rover.</t>
+          <t>Giờ cậu có thể thay đổi ngoại hình của Rover rồi đấy.</t>
         </is>
       </c>
     </row>
@@ -17738,7 +17738,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Bây giờ bạn có thể thay đổi Ngoại Hình của Rover.</t>
+          <t>Giờ cậu có thể thay đổi ngoại hình của Rover rồi đấy.</t>
         </is>
       </c>
     </row>
@@ -17803,7 +17803,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Bây giờ bạn có thể thay đổi Ngoại Hình của Rover.</t>
+          <t>Giờ cậu có thể thay đổi ngoại hình của Rover rồi đấy.</t>
         </is>
       </c>
     </row>
@@ -17868,7 +17868,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>&lt;texture=/Game/Aki/UI/UIResources/Common/Image/UiIconPcBtn/T_IconPcBtn_KeyAlt_UI.T_IconPcBtn_KeyAlt_UI/&gt;+&lt;texture=/Game/Aki/UI/UIResources/Common/Image/UiIconPcBtn/T_IconPcBtn_KeyC_UI.T_IconPcBtn_KeyC_UI/&gt; để thoát Immersion Mode</t>
+          <t>Nhấn &lt;texture=/Game/Aki/UI/UIResources/Common/Image/UiIconPcBtn/T_IconPcBtn_KeyAlt_UI.T_IconPcBtn_KeyAlt_UI/&gt;+&lt;texture=/Game/Aki/UI/UIResources/Common/Image/UiIconPcBtn/T_IconPcBtn_KeyC_UI.T_IconPcBtn_KeyC_UI/&gt; để thoát Chế Độ Hòa Nhập</t>
         </is>
       </c>
     </row>
@@ -17933,7 +17933,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>{0}+{1} to exit Immersion Mode</t>
+          <t>Nhấn {0}+{1} để thoát Chế Độ Hòa Nhập</t>
         </is>
       </c>
     </row>
@@ -17998,7 +17998,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Nhấn để thoát Immersion Mode</t>
+          <t>Nhấn để thoát Chế độ Hòa Nhập</t>
         </is>
       </c>
     </row>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Chọn một màu và nhuộm các khối có màu khác bằng màu đó</t>
+          <t>Chọn một màu và nhuộm các khối khác màu với nó</t>
         </is>
       </c>
     </row>
@@ -18128,7 +18128,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Chọn một màu và nhuộm các khối có màu khác bằng màu đó</t>
+          <t>Chọn một màu và nhuộm các khối khác màu với nó</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Chọn một màu và nhuộm các khối có màu khác bằng màu đó</t>
+          <t>Chọn một màu và nhuộm các khối khác màu với nó</t>
         </is>
       </c>
     </row>
@@ -18453,7 +18453,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Nhuộm tất cả các khối cùng màu với màu mục tiêu trong số bước giới hạn</t>
+          <t>Nhuộm tất cả các khối theo màu mục tiêu trong số bước giới hạn</t>
         </is>
       </c>
     </row>
@@ -18518,7 +18518,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Nhuộm tất cả các khối cùng màu với màu mục tiêu trong số bước giới hạn</t>
+          <t>Nhuộm tất cả các khối theo màu mục tiêu trong số bước giới hạn</t>
         </is>
       </c>
     </row>
@@ -18583,7 +18583,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Nhuộm tất cả các khối cùng màu với màu mục tiêu trong số bước giới hạn</t>
+          <t>Nhuộm tất cả các khối theo màu mục tiêu trong số bước giới hạn</t>
         </is>
       </c>
     </row>
@@ -18648,7 +18648,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Dùng {0} để biến thành Plushie Echo</t>
+          <t>Dùng {0} để hóa thân thành Plushie Echo.</t>
         </is>
       </c>
     </row>
@@ -18778,7 +18778,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Đổi thưởng tại cửa hàng</t>
+          <t>Nhận thưởng tại cửa hàng</t>
         </is>
       </c>
     </row>
@@ -18843,7 +18843,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Đổi thưởng tại cửa hàng</t>
+          <t>Nhận thưởng tại cửa hàng</t>
         </is>
       </c>
     </row>
@@ -18908,7 +18908,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Đổi thưởng tại cửa hàng</t>
+          <t>Nhận thưởng tại cửa hàng</t>
         </is>
       </c>
     </row>
@@ -18973,7 +18973,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Dùng {0} để nâng khối nặng lên kích hoạt cơ chế</t>
+          <t>Dùng {0} để nâng khối nặng lên kích hoạt cơ chế.</t>
         </is>
       </c>
     </row>
@@ -19038,7 +19038,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Dùng {0} để nâng khối nặng lên kích hoạt cơ chế</t>
+          <t>Dùng {0} để nâng khối nặng lên kích hoạt cơ chế.</t>
         </is>
       </c>
     </row>
@@ -19103,7 +19103,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Invite bạn bè cùng chia sẻ khoảnh khắc để nhận phần thưởng hậu hĩnh</t>
+          <t>Mời bạn bè cùng tận hưởng khoảnh khắc để nhận thưởng hậu hĩnh</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Invite bạn bè cùng chia sẻ khoảnh khắc để nhận phần thưởng hậu hĩnh</t>
+          <t>Mời bạn bè cùng tận hưởng khoảnh khắc để nhận thưởng hậu hĩnh</t>
         </is>
       </c>
     </row>
@@ -19233,7 +19233,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Invite bạn bè cùng chia sẻ khoảnh khắc để nhận phần thưởng hậu hĩnh</t>
+          <t>Mời bạn bè cùng tận hưởng khoảnh khắc để nhận thưởng hậu hĩnh</t>
         </is>
       </c>
     </row>
@@ -19298,7 +19298,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Nhuộm tất cả khối theo màu mục tiêu</t>
+          <t>Nhuộm tất cả các khối theo màu mục tiêu</t>
         </is>
       </c>
     </row>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Nhuộm tất cả khối theo màu mục tiêu</t>
+          <t>Nhuộm tất cả các khối theo màu mục tiêu</t>
         </is>
       </c>
     </row>
@@ -19428,7 +19428,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Nhuộm tất cả khối theo màu mục tiêu</t>
+          <t>Nhuộm tất cả các khối theo màu mục tiêu</t>
         </is>
       </c>
     </row>
@@ -19493,7 +19493,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Switch đổi hoặc xem Trang phục khác</t>
+          <t>Chuyển hoặc xem Trang phục khác</t>
         </is>
       </c>
     </row>
@@ -19558,7 +19558,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Switch đổi hoặc xem Trang phục khác</t>
+          <t>Chuyển hoặc xem Trang phục khác</t>
         </is>
       </c>
     </row>
@@ -19623,7 +19623,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Switch đổi hoặc xem Trang phục khác</t>
+          <t>Chuyển hoặc xem Trang phục khác</t>
         </is>
       </c>
     </row>
@@ -19688,7 +19688,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Increase Exploration Progress để nhận thưởng</t>
+          <t>Tăng Tiến Độ Thám Hiểm để nhận thưởng.</t>
         </is>
       </c>
     </row>
@@ -19753,7 +19753,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Increase Exploration Progress để nhận thưởng</t>
+          <t>Tăng Tiến Độ Thám Hiểm để nhận thưởng.</t>
         </is>
       </c>
     </row>
@@ -19818,7 +19818,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Increase Exploration Progress để nhận thưởng</t>
+          <t>Tăng Tiến Độ Thám Hiểm để nhận thưởng.</t>
         </is>
       </c>
     </row>
@@ -20078,7 +20078,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Chọn vật phẩm bạn muốn tổng hợp. &lt;color=#8c7e51&gt;Vuốt&lt;/color&gt; để chuyển đổi độ hiếm mong muốn khi tổng hợp.</t>
+          <t>Chọn vật phẩm muốn tổng hợp. &lt;color=#8c7e51&gt;Vuốt&lt;/color&gt; để chuyển đổi độ hiếm mong muốn khi tổng hợp</t>
         </is>
       </c>
     </row>
@@ -20143,7 +20143,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Chọn vật phẩm bạn muốn tổng hợp. &lt;color=#8c7e51&gt;Vuốt&lt;/color&gt; để chuyển đổi độ hiếm mong muốn khi tổng hợp.</t>
+          <t>Chọn vật phẩm muốn tổng hợp. &lt;color=#8c7e51&gt;Vuốt&lt;/color&gt; để chuyển đổi độ hiếm mong muốn khi tổng hợp</t>
         </is>
       </c>
     </row>
@@ -20208,7 +20208,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Chọn vật phẩm bạn muốn tổng hợp. &lt;color=#8c7e51&gt;Vuốt&lt;/color&gt; để chuyển đổi độ hiếm mong muốn khi tổng hợp.</t>
+          <t>Chọn vật phẩm muốn tổng hợp. &lt;color=#8c7e51&gt;Vuốt&lt;/color&gt; để chuyển đổi độ hiếm mong muốn khi tổng hợp</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Chuyển đổi cho phép bạn đổi vật liệu thành một loại cụ thể</t>
+          <t>Chức năng Chuyển Đổi cho phép bạn biến đổi vật liệu thành một loại cụ thể</t>
         </is>
       </c>
     </row>
@@ -20338,7 +20338,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Chuyển đổi cho phép bạn đổi vật liệu thành một loại cụ thể</t>
+          <t>Chức năng Chuyển Đổi cho phép bạn biến đổi vật liệu thành một loại cụ thể</t>
         </is>
       </c>
     </row>
@@ -20403,7 +20403,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Chuyển đổi cho phép bạn đổi vật liệu thành một loại cụ thể</t>
+          <t>Chức năng Chuyển Đổi cho phép bạn biến đổi vật liệu thành một loại cụ thể</t>
         </is>
       </c>
     </row>
@@ -20468,7 +20468,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Chương mới đã mở khóa. Trải nghiệm ngay.</t>
+          <t>Mở Khóa Chương Mới. Trải nghiệm ngay.</t>
         </is>
       </c>
     </row>
@@ -20533,7 +20533,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Chương mới đã mở khóa. Trải nghiệm ngay.</t>
+          <t>Mở Khóa Chương Mới. Trải nghiệm ngay.</t>
         </is>
       </c>
     </row>
@@ -20598,7 +20598,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Chương mới đã mở khóa. Trải nghiệm ngay.</t>
+          <t>Mở Khóa Chương Mới. Trải nghiệm ngay.</t>
         </is>
       </c>
     </row>
@@ -20858,7 +20858,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Nhấn nút Hợp Tác để kiểm tra trạng thái chế độ.</t>
+          <t>Nhấn nút Đồng Đội để kiểm tra trạng thái chế độ.</t>
         </is>
       </c>
     </row>
@@ -20923,7 +20923,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Nhấn nút Hợp Tác để kiểm tra trạng thái chế độ.</t>
+          <t>Nhấn nút Đồng Đội để kiểm tra trạng thái chế độ.</t>
         </is>
       </c>
     </row>
@@ -20988,7 +20988,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Nhấn nút Hợp Tác để kiểm tra trạng thái chế độ.</t>
+          <t>Nhấn nút Đồng Đội để kiểm tra trạng thái chế độ.</t>
         </is>
       </c>
     </row>
@@ -21053,7 +21053,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Tìm Echo đủ điều kiện qua "Gợi ý".</t>
+          <t>Tìm Echo phù hợp qua mục "Gợi ý".</t>
         </is>
       </c>
     </row>
@@ -21118,7 +21118,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Tìm Echo đủ điều kiện qua "Gợi ý".</t>
+          <t>Tìm Echo phù hợp qua mục "Gợi ý".</t>
         </is>
       </c>
     </row>
@@ -21183,7 +21183,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Tìm Echo đủ điều kiện qua "Gợi ý".</t>
+          <t>Tìm Echo phù hợp qua mục "Gợi ý".</t>
         </is>
       </c>
     </row>
@@ -21248,7 +21248,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Enter sân khấu để bắt đầu thử thách.</t>
+          <t>Bước lên sân khấu để bắt đầu thử thách</t>
         </is>
       </c>
     </row>
@@ -21313,7 +21313,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Enter sân khấu để bắt đầu thử thách.</t>
+          <t>Bước lên sân khấu để bắt đầu thử thách</t>
         </is>
       </c>
     </row>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Enter sân khấu để bắt đầu thử thách.</t>
+          <t>Bước lên sân khấu để bắt đầu thử thách</t>
         </is>
       </c>
     </row>
@@ -21443,7 +21443,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Xem Report môi trường hiện tại.</t>
+          <t>Xem Báo Cáo Môi Trường hiện tại.</t>
         </is>
       </c>
     </row>
@@ -21508,7 +21508,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Xem Report môi trường hiện tại.</t>
+          <t>Xem Báo Cáo Môi Trường hiện tại.</t>
         </is>
       </c>
     </row>
@@ -21573,7 +21573,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Xem Report môi trường hiện tại.</t>
+          <t>Xem Báo Cáo Môi Trường hiện tại.</t>
         </is>
       </c>
     </row>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Triển khai ít nhất 3 Resonators cho mỗi nửa thử thách.</t>
+          <t>Triển khai ít nhất 3 Resonator cho mỗi nửa thử thách.</t>
         </is>
       </c>
     </row>
@@ -21703,7 +21703,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Triển khai ít nhất 3 Resonators cho mỗi nửa thử thách.</t>
+          <t>Triển khai ít nhất 3 Resonator cho mỗi nửa thử thách.</t>
         </is>
       </c>
     </row>
@@ -21768,7 +21768,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Triển khai ít nhất 3 Resonators cho mỗi nửa thử thách.</t>
+          <t>Triển khai ít nhất 3 Resonator cho mỗi nửa thử thách.</t>
         </is>
       </c>
     </row>
@@ -21833,7 +21833,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Chọn Token.</t>
+          <t>Chọn Token</t>
         </is>
       </c>
     </row>
@@ -21898,7 +21898,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>{0} Chọn Một Token.</t>
+          <t>Chọn một Token.</t>
         </is>
       </c>
     </row>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Chọn Token.</t>
+          <t>Chọn Token</t>
         </is>
       </c>
     </row>
@@ -22028,7 +22028,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Đội hình đặt trước đã sẵn sàng.</t>
+          <t>Đã có đội hình cài đặt sẵn.</t>
         </is>
       </c>
     </row>
@@ -22093,7 +22093,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Đội hình đặt trước đã sẵn sàng.</t>
+          <t>Đã có đội hình cài đặt sẵn.</t>
         </is>
       </c>
     </row>
@@ -22158,7 +22158,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Đội hình đặt trước đã sẵn sàng.</t>
+          <t>Đã có đội hình cài đặt sẵn.</t>
         </is>
       </c>
     </row>
@@ -22223,7 +22223,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Token được chia thành 2 loại dựa trên số lần sử dụng giới hạn hoặc không giới hạn.</t>
+          <t>Mãnh được chia thành 2 loại dựa trên số lần sử dụng giới hạn hoặc không giới hạn.</t>
         </is>
       </c>
     </row>
@@ -22288,7 +22288,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Token được chia thành 2 loại dựa trên số lần sử dụng giới hạn hoặc không giới hạn.</t>
+          <t>Mãnh được chia thành 2 loại dựa trên số lần sử dụng giới hạn hoặc không giới hạn.</t>
         </is>
       </c>
     </row>
@@ -22353,7 +22353,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Token được chia thành 2 loại dựa trên số lần sử dụng giới hạn hoặc không giới hạn.</t>
+          <t>Mãnh được chia thành 2 loại dựa trên số lần sử dụng giới hạn hoặc không giới hạn.</t>
         </is>
       </c>
     </row>
@@ -22418,7 +22418,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Hoàn thành Requests Fishing để nhận Fame.</t>
+          <t>Hoàn thành Nhiệm Vụ Câu Cá để nhận Danh Vọng.</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Hoàn thành Requests Fishing để nhận Fame.</t>
+          <t>Hoàn thành Nhiệm Vụ Câu Cá để nhận Danh Vọng.</t>
         </is>
       </c>
     </row>
@@ -22548,7 +22548,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Hoàn thành Requests Fishing để nhận Fame.</t>
+          <t>Hoàn thành Nhiệm Vụ Câu Cá để nhận Danh Vọng.</t>
         </is>
       </c>
     </row>
@@ -22613,7 +22613,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Nhấn "Set Sail" để chuẩn bị cho chuyến đi tiếp theo.</t>
+          <t>Nhấn "Khởi Hành" để chuẩn bị cho chuyến đi tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -22678,7 +22678,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>{0} Nhấn "Set Sail" để chuẩn bị cho chuyến đi tiếp theo.</t>
+          <t>Nhấn "Khởi Hành" để chuẩn bị cho chuyến đi tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -22743,7 +22743,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>{0} Nhấn "Set Sail" để chuẩn bị cho chuyến đi tiếp theo.</t>
+          <t>Nhấn "Khởi Hành" để chuẩn bị cho chuyến đi tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -22808,7 +22808,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Board the Gondola Rachel nào. Đi câu cá thôi!</t>
+          <t>Lên thuyền gondola đi Rachel. Đi câu cá nào!</t>
         </is>
       </c>
     </row>
@@ -22873,7 +22873,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>{0} Lên thuyền Gondola Rachel. Đi câu cá thôi!</t>
+          <t>Lên thuyền Gondola Rachel nào. Đi câu cá thôi!</t>
         </is>
       </c>
     </row>
@@ -22938,7 +22938,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Board the Gondola Rachel nào. Đi câu cá thôi!</t>
+          <t>Lên thuyền gondola đi Rachel. Đi câu cá nào!</t>
         </is>
       </c>
     </row>
@@ -23003,7 +23003,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Nhận mẻ câu khi Tiến Độ Fishing đạt tối đa.</t>
+          <t>Kéo cá lên khi Thanh Tiến Độ Câu Cá đạt tối đa.</t>
         </is>
       </c>
     </row>
@@ -23068,7 +23068,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Nhận mẻ câu khi Tiến Độ Fishing đạt tối đa.</t>
+          <t>Kéo cá lên khi Thanh Tiến Độ Câu Cá đạt tối đa.</t>
         </is>
       </c>
     </row>
@@ -23133,7 +23133,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Nhận mẻ câu khi Tiến Độ Fishing đạt tối đa.</t>
+          <t>Kéo cá lên khi Thanh Tiến Độ Câu Cá đạt tối đa.</t>
         </is>
       </c>
     </row>
@@ -23198,7 +23198,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Nhấn nút khi súng giáo nằm trong vùng tô sáng màu xanh để tăng tiến độ.</t>
+          <t>Nhấn nút khi súng lao nằm trong vùng tô xanh để tăng tiến độ.</t>
         </is>
       </c>
     </row>
@@ -23263,7 +23263,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Nhấn nút khi súng giáo nằm trong vùng tô sáng màu xanh để tăng tiến độ.</t>
+          <t>Nhấn nút khi súng lao nằm trong vùng tô xanh để tăng tiến độ.</t>
         </is>
       </c>
     </row>
@@ -23328,7 +23328,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Nhấn nút khi súng giáo nằm trong vùng tô sáng màu xanh để tăng tiến độ.</t>
+          <t>Nhấn nút khi súng lao nằm trong vùng tô xanh để tăng tiến độ.</t>
         </is>
       </c>
     </row>
@@ -23588,7 +23588,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Nhấn nút khi súng móc nằm trong vùng sáng để tăng tiến độ.</t>
+          <t>Nhấn nút khi súng lao nằm trong vùng tô sáng để tăng tiến độ.</t>
         </is>
       </c>
     </row>
@@ -23653,7 +23653,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>{0} Nhấn nút khi súng lao nằm trong vùng sáng để tăng tiến độ.</t>
+          <t>Nhấn nút khi súng phóng lao nằm trong vùng đánh dấu để tăng tiến độ.</t>
         </is>
       </c>
     </row>
@@ -23718,7 +23718,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Nhấn nút khi súng móc nằm trong vùng sáng để tăng tiến độ.</t>
+          <t>Nhấn nút khi súng lao nằm trong vùng tô sáng để tăng tiến độ.</t>
         </is>
       </c>
     </row>
@@ -23783,7 +23783,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Giao nộp vật phẩm yêu cầu để nhận thưởng.</t>
+          <t>Giao số cá đã yêu cầu để nhận thưởng.</t>
         </is>
       </c>
     </row>
@@ -23848,7 +23848,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Giao nộp vật phẩm yêu cầu để nhận thưởng.</t>
+          <t>Giao số cá đã yêu cầu để nhận thưởng.</t>
         </is>
       </c>
     </row>
@@ -23913,7 +23913,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Giao nộp vật phẩm yêu cầu để nhận thưởng.</t>
+          <t>Giao số cá đã yêu cầu để nhận thưởng.</t>
         </is>
       </c>
     </row>
@@ -23978,7 +23978,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Chỉ những mẻ đánh bắt được lưu trong khoang hàng mới có thể mang về bến. Hãy sử dụng không gian khoang hàng hạn chế của bạn một cách khôn ngoan.</t>
+          <t>Chỉ những vật phẩm lưu trong khoang hàng mới có thể mang về bến. Hãy sử dụng không gian khoang hạn chế của ngươi một cách khôn ngoan.</t>
         </is>
       </c>
     </row>
@@ -24043,7 +24043,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Chỉ những mẻ đánh bắt được lưu trong khoang hàng mới có thể mang về bến. Hãy sử dụng không gian khoang hàng hạn chế của bạn một cách khôn ngoan.</t>
+          <t>Chỉ những vật phẩm lưu trong khoang hàng mới có thể mang về bến. Hãy sử dụng không gian khoang hạn chế của ngươi một cách khôn ngoan.</t>
         </is>
       </c>
     </row>
@@ -24108,7 +24108,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Chỉ những mẻ đánh bắt được lưu trong khoang hàng mới có thể mang về bến. Hãy sử dụng không gian khoang hàng hạn chế của bạn một cách khôn ngoan.</t>
+          <t>Chỉ những vật phẩm lưu trong khoang hàng mới có thể mang về bến. Hãy sử dụng không gian khoang hạn chế của ngươi một cách khôn ngoan.</t>
         </is>
       </c>
     </row>
@@ -24173,7 +24173,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Chọn hoặc kéo chiến lợi phẩm vào kho để lưu trữ.</t>
+          <t>Chọn hoặc kéo con mồi vào để lưu trong khoang hàng.</t>
         </is>
       </c>
     </row>
@@ -24238,7 +24238,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Kéo chiến lợi phẩm vào khoang hàng theo hướng dẫn phía trên để lưu trữ</t>
+          <t>Kéo vật phẩm vào để lưu trữ trong khoang hàng theo hướng dẫn phía trên</t>
         </is>
       </c>
     </row>
@@ -24303,7 +24303,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Chọn hoặc kéo chiến lợi phẩm vào kho để lưu trữ.</t>
+          <t>Chọn hoặc kéo con mồi vào để lưu trong khoang hàng.</t>
         </is>
       </c>
     </row>
@@ -24368,7 +24368,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Quản lý không gian Cargo bằng cách di chuyển hoặc xoay chiến lợi phẩm.</t>
+          <t>Sắp xếp không gian Cargo bằng cách di chuyển hoặc xoay chiến lợi phẩm của bạn.</t>
         </is>
       </c>
     </row>
@@ -24433,7 +24433,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Quản lý không gian Cargo bằng cách di chuyển hoặc xoay chiến lợi phẩm.</t>
+          <t>Sắp xếp không gian Cargo bằng cách di chuyển hoặc xoay chiến lợi phẩm của bạn.</t>
         </is>
       </c>
     </row>
@@ -24498,7 +24498,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Quản lý không gian Cargo bằng cách di chuyển hoặc xoay chiến lợi phẩm.</t>
+          <t>Sắp xếp không gian Cargo bằng cách di chuyển hoặc xoay chiến lợi phẩm của bạn.</t>
         </is>
       </c>
     </row>
@@ -24563,7 +24563,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Xem thông tin mẻ câu của bạn tại đây.</t>
+          <t>Xem thông tin về con mồi của cậu tại đây.</t>
         </is>
       </c>
     </row>
@@ -24628,7 +24628,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Xem thông tin mẻ câu của bạn tại đây.</t>
+          <t>Xem thông tin về con mồi của cậu tại đây.</t>
         </is>
       </c>
     </row>
@@ -24693,7 +24693,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Xem thông tin mẻ câu của bạn tại đây.</t>
+          <t>Xem thông tin về con mồi của cậu tại đây.</t>
         </is>
       </c>
     </row>
@@ -24758,7 +24758,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Increase Fame để trở thành Pro Angler!</t>
+          <t>Tăng Danh Vọng để trở thành Câu Cá Pro!</t>
         </is>
       </c>
     </row>
@@ -24823,7 +24823,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Increase Fame để trở thành Pro Angler!</t>
+          <t>Tăng Danh Vọng để trở thành Câu Cá Pro!</t>
         </is>
       </c>
     </row>
@@ -24888,7 +24888,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Increase Fame để trở thành Pro Angler!</t>
+          <t>Tăng Danh Vọng để trở thành Câu Cá Pro!</t>
         </is>
       </c>
     </row>
@@ -24953,7 +24953,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Sell mẻ đánh bắt của bạn tại cửa hàng bến tàu.</t>
+          <t>Bán chiến lợi phẩm của cậu tại cửa hàng bến cảng.</t>
         </is>
       </c>
     </row>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>{0} Sell mẻ câu của bạn tại cửa hàng bến tàu.</t>
+          <t>Bán chiến lợi phẩm tại cửa hàng bến tàu.</t>
         </is>
       </c>
     </row>
@@ -25083,7 +25083,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Sell mẻ đánh bắt của bạn tại cửa hàng bến tàu.</t>
+          <t>Bán chiến lợi phẩm của cậu tại cửa hàng bến cảng.</t>
         </is>
       </c>
     </row>
@@ -25148,7 +25148,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Sell tất cả chiến lợi phẩm đang lưu trong hàng hóa.</t>
+          <t>Bán hết số hàng hóa đang lưu trong kho.</t>
         </is>
       </c>
     </row>
@@ -25213,7 +25213,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Sell toàn bộ {0} mẻ đánh bắt đang lưu trong hàng hóa.</t>
+          <t>Bán toàn bộ chiến lợi phẩm đang lưu trong kho hàng.</t>
         </is>
       </c>
     </row>
@@ -25278,7 +25278,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Sell tất cả chiến lợi phẩm đang lưu trong hàng hóa.</t>
+          <t>Bán hết số hàng hóa đang lưu trong kho.</t>
         </is>
       </c>
     </row>
@@ -25343,7 +25343,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Dùng Xu Câu Cá để mua dụng cụ câu.</t>
+          <t>Dùng Fishery Coins để mua dụng cụ câu cá</t>
         </is>
       </c>
     </row>
@@ -25408,7 +25408,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>{0} Dùng Xu Khu Đánh Cá để mua dụng cụ câu cá.</t>
+          <t>{0} Dùng Xu Khu Nuôi Cá để mua dụng cụ câu cá.</t>
         </is>
       </c>
     </row>
@@ -25473,7 +25473,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Dùng Xu Câu Cá để mua dụng cụ câu.</t>
+          <t>Dùng Fishery Coins để mua dụng cụ câu cá</t>
         </is>
       </c>
     </row>
@@ -25538,7 +25538,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Nâng cấp Kỹ Năng Fishing của Resonator để tăng hiệu suất câu cá.</t>
+          <t>Nâng cấp Kỹ Năng Câu Cá của Resonator để tăng hiệu suất câu cá.</t>
         </is>
       </c>
     </row>
@@ -25603,7 +25603,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Nâng cấp Kỹ Năng Fishing của Resonator để tăng hiệu suất câu cá.</t>
+          <t>Nâng cấp Kỹ Năng Câu Cá của Resonator để tăng hiệu suất câu cá.</t>
         </is>
       </c>
     </row>
@@ -25668,7 +25668,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Nâng cấp Kỹ Năng Fishing của Resonator để tăng hiệu suất câu cá.</t>
+          <t>Nâng cấp Kỹ Năng Câu Cá của Resonator để tăng hiệu suất câu cá.</t>
         </is>
       </c>
     </row>
@@ -25733,7 +25733,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Hoàn thành yêu cầu để nhận phần thưởng giới hạn.</t>
+          <t>Hoàn thành yêu cầu để nhận phần thưởng giới hạn thời gian.</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Hoàn thành yêu cầu để nhận phần thưởng giới hạn.</t>
+          <t>Hoàn thành yêu cầu để nhận phần thưởng giới hạn thời gian.</t>
         </is>
       </c>
     </row>
@@ -25863,7 +25863,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Hoàn thành yêu cầu để nhận phần thưởng giới hạn.</t>
+          <t>Hoàn thành yêu cầu để nhận phần thưởng giới hạn thời gian.</t>
         </is>
       </c>
     </row>
@@ -25928,7 +25928,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Sát thương nhận vào tăng dần theo thời gian. Hãy lên kế hoạch lộ trình phù hợp.</t>
+          <t>Sát thương nhận vào tăng dần theo thời gian. Hãy lên lộ trình cẩn thận.</t>
         </is>
       </c>
     </row>
@@ -25993,7 +25993,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Sát thương nhận vào tăng dần theo thời gian. Hãy lên kế hoạch lộ trình phù hợp.</t>
+          <t>Sát thương nhận vào tăng dần theo thời gian. Hãy lên lộ trình cẩn thận.</t>
         </is>
       </c>
     </row>
@@ -26058,7 +26058,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Sát thương nhận vào tăng dần theo thời gian. Hãy lên kế hoạch lộ trình phù hợp.</t>
+          <t>Sát thương nhận vào tăng dần theo thời gian. Hãy lên lộ trình cẩn thận.</t>
         </is>
       </c>
     </row>
@@ -26123,7 +26123,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Kiểm tra [Dreamscape Aid] hiện tại tại đây.</t>
+          <t>Kiểm tra [Dreamscape Aid] ở đây.</t>
         </is>
       </c>
     </row>
@@ -26188,7 +26188,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Kiểm tra [Dreamscape Aid] hiện tại tại đây.</t>
+          <t>Kiểm tra [Dreamscape Aid] ở đây.</t>
         </is>
       </c>
     </row>
@@ -26253,7 +26253,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Kiểm tra [Dreamscape Aid] hiện tại tại đây.</t>
+          <t>Kiểm tra [Dreamscape Aid] ở đây.</t>
         </is>
       </c>
     </row>
@@ -26318,7 +26318,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Nhận Astrites và nhiều phần thưởng khác.</t>
+          <t>Nhận Astrites cùng nhiều phần thưởng khác.</t>
         </is>
       </c>
     </row>
@@ -26383,7 +26383,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Nhận Astrites và nhiều phần thưởng khác.</t>
+          <t>Nhận Astrites cùng nhiều phần thưởng khác.</t>
         </is>
       </c>
     </row>
@@ -26448,7 +26448,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Nhận Astrites và nhiều phần thưởng khác.</t>
+          <t>Nhận Astrites cùng nhiều phần thưởng khác.</t>
         </is>
       </c>
     </row>
@@ -26513,7 +26513,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Xem chi tiết sự kiện thường trực "Fantasies of the Thousand Gateways" tại đây.</t>
+          <t>Xem chi tiết Sự Kiện Thường Xuyên "Ảo Ảnh Ngàn Cánh Cổng" tại đây.</t>
         </is>
       </c>
     </row>
@@ -26578,7 +26578,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Xem chi tiết sự kiện thường trực "Fantasies of the Thousand Gateways" tại đây.</t>
+          <t>Xem chi tiết Sự Kiện Thường Xuyên "Ảo Ảnh Ngàn Cánh Cổng" tại đây.</t>
         </is>
       </c>
     </row>
@@ -26643,7 +26643,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Xem chi tiết sự kiện thường trực "Fantasies of the Thousand Gateways" tại đây.</t>
+          <t>Xem chi tiết Sự Kiện Thường Xuyên "Ảo Ảnh Ngàn Cánh Cổng" tại đây.</t>
         </is>
       </c>
     </row>
@@ -26903,7 +26903,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Thử thách mới sẽ mở sau khi giai đoạn hiện tại kết thúc.</t>
+          <t>Các thử thách mới sẽ mở sau khi giai đoạn hiện tại kết thúc.</t>
         </is>
       </c>
     </row>
@@ -26968,7 +26968,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Thử thách mới sẽ mở sau khi giai đoạn hiện tại kết thúc.</t>
+          <t>Các thử thách mới sẽ mở sau khi giai đoạn hiện tại kết thúc.</t>
         </is>
       </c>
     </row>
@@ -27033,7 +27033,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Thử thách mới sẽ mở sau khi giai đoạn hiện tại kết thúc.</t>
+          <t>Các thử thách mới sẽ mở sau khi giai đoạn hiện tại kết thúc.</t>
         </is>
       </c>
     </row>
@@ -27098,7 +27098,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Đã mở khóa mục Chỉ mục mới. Dùng Track để đánh dấu vật phẩm trên bản đồ.</t>
+          <t>Mục Chỉ Mục Mới đã mở khóa. Sử dụng Theo Dõi để đánh dấu vật phẩm trên bản đồ.</t>
         </is>
       </c>
     </row>
@@ -27163,7 +27163,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Đã mở khóa mục Chỉ mục mới. Dùng Track để đánh dấu vật phẩm trên bản đồ.</t>
+          <t>Mục Chỉ Mục Mới đã mở khóa. Sử dụng Theo Dõi để đánh dấu vật phẩm trên bản đồ.</t>
         </is>
       </c>
     </row>
@@ -27228,7 +27228,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Đã mở khóa mục Chỉ mục mới. Dùng Track để đánh dấu vật phẩm trên bản đồ.</t>
+          <t>Mục Chỉ Mục Mới đã mở khóa. Sử dụng Theo Dõi để đánh dấu vật phẩm trên bản đồ.</t>
         </is>
       </c>
     </row>
@@ -27293,7 +27293,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Yêu cầu hoàn tất. Tiến hành giao hàng.</t>
+          <t>Hoàn thành nhiệm vụ. Tiến hành giao nộp chiến lợi phẩm.</t>
         </is>
       </c>
     </row>
@@ -27358,7 +27358,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>{0} Yêu cầu hoàn tất. Tiến hành giao mẻ câu</t>
+          <t>Yêu cầu hoàn tất. Tiến hành giao chiến lợi phẩm</t>
         </is>
       </c>
     </row>
@@ -27423,7 +27423,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Yêu cầu hoàn tất. Tiến hành giao hàng</t>
+          <t>Hoàn thành nhiệm vụ. Tiến hành giao nộp chiến lợi phẩm</t>
         </is>
       </c>
     </row>
@@ -27488,7 +27488,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Giao nộp vật phẩm yêu cầu để nhận thưởng.</t>
+          <t>Giao mẻ đánh bắt được để nhận thưởng.</t>
         </is>
       </c>
     </row>
@@ -27553,7 +27553,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>{0} Giao nộp yêu cầu để nhận thưởng nhiệm vụ.</t>
+          <t>Giao nộp yêu cầu để nhận thưởng nhiệm vụ.</t>
         </is>
       </c>
     </row>
@@ -27618,7 +27618,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Giao nộp vật phẩm yêu cầu để nhận thưởng.</t>
+          <t>Giao mẻ đánh bắt được để nhận thưởng.</t>
         </is>
       </c>
     </row>
@@ -27683,7 +27683,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Một số yêu cầu chỉ khả dụng sau khi mở khóa một số Kỹ Năng Fishing nhất định.</t>
+          <t>Một số yêu cầu chỉ có thể thực hiện sau khi mở khóa một số Kỹ Năng Câu Cá nhất định.</t>
         </is>
       </c>
     </row>
@@ -27748,7 +27748,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Một số yêu cầu chỉ khả dụng sau khi mở khóa một số Kỹ Năng Fishing nhất định.</t>
+          <t>Một số yêu cầu chỉ có thể thực hiện sau khi mở khóa một số Kỹ Năng Câu Cá nhất định.</t>
         </is>
       </c>
     </row>
@@ -27813,7 +27813,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Một số yêu cầu chỉ khả dụng sau khi mở khóa một số Kỹ Năng Fishing nhất định.</t>
+          <t>Một số yêu cầu chỉ có thể thực hiện sau khi mở khóa một số Kỹ Năng Câu Cá nhất định.</t>
         </is>
       </c>
     </row>
@@ -27878,7 +27878,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Nâng cấp Fishing Ability để mở khóa yêu cầu này.</t>
+          <t>Nâng cấp Kỹ Năng Câu Cá để nhận nhiệm vụ này.</t>
         </is>
       </c>
     </row>
@@ -27943,7 +27943,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>{0} Nâng Cấp Fishing Ability để mở khóa yêu cầu này.</t>
+          <t>Nâng cấp Khả Năng Câu Cá để mở khóa nhiệm vụ này.</t>
         </is>
       </c>
     </row>
@@ -28008,7 +28008,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Nâng cấp Fishing Ability để mở khóa yêu cầu này.</t>
+          <t>Nâng cấp Kỹ Năng Câu Cá để nhận nhiệm vụ này.</t>
         </is>
       </c>
     </row>
@@ -28073,7 +28073,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Nâng cấp Khả năng Fishing để mở khóa thêm nhiều buff câu cá.</t>
+          <t>Nâng cấp Kỹ Năng Câu Cá để mở khóa thêm nhiều hiệu ứng hỗ trợ câu cá.</t>
         </is>
       </c>
     </row>
@@ -28138,7 +28138,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>{0}Nâng cao Khả Năng Fishing để mở khóa thêm nhiều buff câu cá.</t>
+          <t>Nâng cấp Khả Năng Câu Cá để mở khóa thêm các hiệu ứng hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -28203,7 +28203,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Nâng cấp Khả năng Fishing để mở khóa thêm nhiều buff câu cá.</t>
+          <t>Nâng cấp Kỹ Năng Câu Cá để mở khóa thêm nhiều hiệu ứng hỗ trợ câu cá.</t>
         </is>
       </c>
     </row>
@@ -28268,7 +28268,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Các khu vực câu cá bổ sung đã mở. Chuẩn bị ra khơi thôi!</t>
+          <t>Các khu vực câu cá mới đã mở. Chuẩn bị ra khơi thôi!</t>
         </is>
       </c>
     </row>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>{0} Các khu vực câu cá bổ sung hiện đã mở. Hãy chuẩn bị ra khơi!</t>
+          <t>{0} Các khu vực câu cá mới đã mở. Chuẩn bị ra khơi nào!</t>
         </is>
       </c>
     </row>
@@ -28398,7 +28398,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Các khu vực câu cá bổ sung đã mở. Chuẩn bị ra khơi thôi!</t>
+          <t>Các khu vực câu cá mới đã mở. Chuẩn bị ra khơi thôi!</t>
         </is>
       </c>
     </row>
@@ -28463,7 +28463,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Không có yêu cầu nào khả dụng. Đến lúc quay về bến tàu.</t>
+          <t>Không có yêu cầu nào khả dụng. Đến lúc quay về bến thôi.</t>
         </is>
       </c>
     </row>
@@ -28528,7 +28528,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>{0} Không có yêu cầu nào khả dụng. Đến lúc quay về bến tàu.</t>
+          <t>{0} Không có yêu cầu nào khả dụng. Đến lúc quay về bến tàu thôi.</t>
         </is>
       </c>
     </row>
@@ -28593,7 +28593,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Không có yêu cầu nào khả dụng. Đến lúc quay về bến tàu.</t>
+          <t>Không có yêu cầu nào khả dụng. Đến lúc quay về bến thôi.</t>
         </is>
       </c>
     </row>
@@ -28658,7 +28658,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Enter trạng thái [Lucid Dream] khi Dreamscape Energy đầy và nhận thưởng khả năng.</t>
+          <t>Vào trạng thái [Giấc Mơ Sáng Suốt] khi Năng Lượng Cảnh Mộng đạt tối đa và nhận thưởng khả năng.</t>
         </is>
       </c>
     </row>
@@ -28723,7 +28723,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Enter trạng thái [Lucid Dream] khi Dreamscape Energy đầy và nhận thưởng khả năng.</t>
+          <t>Vào trạng thái [Giấc Mơ Sáng Suốt] khi Năng Lượng Cảnh Mộng đạt tối đa và nhận thưởng khả năng.</t>
         </is>
       </c>
     </row>
@@ -28788,7 +28788,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Enter trạng thái [Lucid Dream] khi Dreamscape Energy đầy và nhận thưởng khả năng.</t>
+          <t>Vào trạng thái [Giấc Mơ Sáng Suốt] khi Năng Lượng Cảnh Mộng đạt tối đa và nhận thưởng khả năng.</t>
         </is>
       </c>
     </row>
@@ -28853,7 +28853,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Các phép ẩn dụ được đánh dấu Sức Mạnh Giấc Mơ sẽ được tăng cường trong trạng thái [Lucid Dream].</t>
+          <t>Ẩn Dụ có dấu hiệu Sức Mạnh Giấc Mơ sẽ được tăng cường trong trạng thái [Giấc Mơ Sáng Tỏ].</t>
         </is>
       </c>
     </row>
@@ -28918,7 +28918,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Các phép ẩn dụ được đánh dấu Sức Mạnh Giấc Mơ sẽ được tăng cường trong trạng thái [Lucid Dream].</t>
+          <t>Ẩn Dụ có dấu hiệu Sức Mạnh Giấc Mơ sẽ được tăng cường trong trạng thái [Giấc Mơ Sáng Tỏ].</t>
         </is>
       </c>
     </row>
@@ -28983,7 +28983,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Các phép ẩn dụ được đánh dấu Sức Mạnh Giấc Mơ sẽ được tăng cường trong trạng thái [Lucid Dream].</t>
+          <t>Ẩn Dụ có dấu hiệu Sức Mạnh Giấc Mơ sẽ được tăng cường trong trạng thái [Giấc Mơ Sáng Tỏ].</t>
         </is>
       </c>
     </row>
@@ -29048,7 +29048,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>{0} Dùng đèn để di chuyển giữa các chiều không gian.</t>
+          <t>Dùng đèn để di chuyển giữa các chiều không gian.</t>
         </is>
       </c>
     </row>
@@ -29113,7 +29113,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Dùng đèn để di chuyển giữa các chiều không gian.</t>
+          <t>Dùng đèn để di chuyển giữa các chiều không gian</t>
         </is>
       </c>
     </row>
@@ -29373,7 +29373,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Tính năng Bán Nhanh đã mở khóa. Bạn có thể bán trực tiếp chiến lợi phẩm đã chọn từ hàng hóa.</t>
+          <t>Đã mở khóa Bán Nhanh. Giờ cậu có thể bán trực tiếp chiến lợi phẩm đã chọn từ kho hàng.</t>
         </is>
       </c>
     </row>
@@ -29438,7 +29438,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>{0} Bán Nhanh đã mở khóa. Giờ bạn có thể bán trực tiếp lô hàng đã chọn từ khoang chứa.</t>
+          <t>Tính năng Bán Nhanh đã mở khóa. Giờ bạn có thể bán trực tiếp chiến lợi phẩm đã chọn từ hàng hóa.</t>
         </is>
       </c>
     </row>
@@ -29503,7 +29503,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Tính năng Bán Nhanh đã mở khóa. Bạn có thể bán trực tiếp chiến lợi phẩm đã chọn từ hàng hóa.</t>
+          <t>Đã mở khóa Bán Nhanh. Giờ cậu có thể bán trực tiếp chiến lợi phẩm đã chọn từ kho hàng.</t>
         </is>
       </c>
     </row>
@@ -29568,7 +29568,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Xem chi tiết Fishing Ability.</t>
+          <t>Xem chi tiết Kỹ Năng Câu Cá.</t>
         </is>
       </c>
     </row>
@@ -29633,7 +29633,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Xem chi tiết Fishing Ability.</t>
+          <t>Xem chi tiết Kỹ Năng Câu Cá.</t>
         </is>
       </c>
     </row>
@@ -29698,7 +29698,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Xem chi tiết Fishing Ability.</t>
+          <t>Xem chi tiết Kỹ Năng Câu Cá.</t>
         </is>
       </c>
     </row>
@@ -29763,7 +29763,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>{0} View trạng thái chơi Co-op qua Terminal.</t>
+          <t>Xem trạng thái chơi Co-op qua Thiết bị đầu cuối.</t>
         </is>
       </c>
     </row>
@@ -29828,7 +29828,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Nhấn nút Hợp Tác để kiểm tra trạng thái chế độ.</t>
+          <t>Nhấn nút Đồng Đội để kiểm tra trạng thái chế độ.</t>
         </is>
       </c>
     </row>
@@ -29893,7 +29893,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Các Restoration Station trên bản đồ có thể hồi sinh Resonators và phục hồi HP.</t>
+          <t>Các Trạm Phục Hồi trên bản đồ có thể hồi sinh Resonator và khôi phục HP</t>
         </is>
       </c>
     </row>
@@ -29958,7 +29958,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Các Restoration Station trên bản đồ có thể hồi sinh Resonators và phục hồi HP.</t>
+          <t>Các Trạm Phục Hồi trên bản đồ có thể hồi sinh Resonator và khôi phục HP</t>
         </is>
       </c>
     </row>
@@ -30023,7 +30023,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Các Restoration Station trên bản đồ có thể hồi sinh Resonators và phục hồi HP.</t>
+          <t>Các Trạm Phục Hồi trên bản đồ có thể hồi sinh Resonator và khôi phục HP</t>
         </is>
       </c>
     </row>
@@ -30088,7 +30088,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Truy cập "Fantasies of the Thousand Gateways" qua Sổ tay.</t>
+          <t>Vào "Fantasies of the Thousand Gateways" qua Sổ tay Hướng dẫn.</t>
         </is>
       </c>
     </row>
@@ -30153,7 +30153,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>{0} Truy cập "Fantasies of the Thousand Gateways" qua Sổ tay.</t>
+          <t>Truy cập "Ảo Ảnh Nghìn Cánh Cổng" qua Sổ Hướng Dẫn.</t>
         </is>
       </c>
     </row>
@@ -30218,7 +30218,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Truy cập để xem chi tiết Sự Kiện Thường Xuyên "Ảo Ảnh Nghìn Cánh Cổng".</t>
+          <t>Tiến vào để xem chi tiết Sự Kiện Thường Xuyên "Ảo Ảnh Ngàn Cánh Cửa".</t>
         </is>
       </c>
     </row>
@@ -30283,7 +30283,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Truy cập "Fantasies of the Thousand Gateways" qua Sổ tay.</t>
+          <t>Vào "Fantasies of the Thousand Gateways" qua Sổ tay Hướng dẫn.</t>
         </is>
       </c>
     </row>
@@ -30348,7 +30348,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>{0} Nhấn để sử dụng Thiết Bị Dọn Dẹp.</t>
+          <t>Nhấn để sử dụng Thiết Bị Dọn Dẹp.</t>
         </is>
       </c>
     </row>
@@ -30413,7 +30413,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Nhấn để sử dụng Thiết bị Dọn dẹp.</t>
+          <t>Nhấn để sử dụng Thiết bị Dọn Dẹp.</t>
         </is>
       </c>
     </row>
@@ -30478,7 +30478,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Thu thập đủ Low-Capacity Variables để mở khóa High-Capacity Variables</t>
+          <t>Thu thập đủ Biến Số Công Suất Thấp để mở khóa Biến Số Công Suất Cao</t>
         </is>
       </c>
     </row>
@@ -30543,7 +30543,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Thu thập đủ Low-Capacity Variables để mở khóa High-Capacity Variables</t>
+          <t>Thu thập đủ Biến Số Công Suất Thấp để mở khóa Biến Số Công Suất Cao</t>
         </is>
       </c>
     </row>
@@ -30608,7 +30608,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Thu thập đủ Low-Capacity Variables để mở khóa High-Capacity Variables</t>
+          <t>Thu thập đủ Biến Số Công Suất Thấp để mở khóa Biến Số Công Suất Cao</t>
         </is>
       </c>
     </row>
@@ -30673,7 +30673,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>{0} Dùng đèn để xua tan bóng tối bao phủ kẻ địch.</t>
+          <t>Dùng đèn để xua tan bóng tối che phủ kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -30738,7 +30738,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Dùng đèn để xua tan bóng tối bao phủ kẻ địch.</t>
+          <t>Dùng đèn xua tan bóng tối che phủ kẻ địch</t>
         </is>
       </c>
     </row>
@@ -30803,7 +30803,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Hoàn thành Crisis Trials để mở khóa Hỗ Trợ Modules dùng trong Disaster Trials.</t>
+          <t>Hoàn thành Thử Thách Khủng Hoảng để mở khóa Mô-đun Hỗ trợ dùng trong Thử Thách Tai Họa.</t>
         </is>
       </c>
     </row>
@@ -30868,7 +30868,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Hoàn thành Crisis Trials để mở khóa Hỗ Trợ Modules dùng trong Disaster Trials.</t>
+          <t>Hoàn thành Thử Thách Khủng Hoảng để mở khóa Mô-đun Hỗ trợ dùng trong Thử Thách Tai Họa.</t>
         </is>
       </c>
     </row>
@@ -30933,7 +30933,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Hoàn thành Crisis Trials để mở khóa Hỗ Trợ Modules dùng trong Disaster Trials.</t>
+          <t>Hoàn thành Thử Thách Khủng Hoảng để mở khóa Mô-đun Hỗ trợ dùng trong Thử Thách Tai Họa.</t>
         </is>
       </c>
     </row>
@@ -30998,7 +30998,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Kiểm tra Mục Tiêu Thử Thách và Phần Thưởng tại đây.</t>
+          <t>Xem Mục Tiêu Thử Thách và Phần Thưởng tại đây.</t>
         </is>
       </c>
     </row>
@@ -31063,7 +31063,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>{0} Check Mục tiêu và Rewards Challenge tại đây.</t>
+          <t>Kiểm tra Mục Tiêu và Phần Thưởng Thử Thách tại đây.</t>
         </is>
       </c>
     </row>
@@ -31128,7 +31128,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Kiểm tra Mục Tiêu Thử Thách và Phần Thưởng tại đây.</t>
+          <t>Xem Mục Tiêu Thử Thách và Phần Thưởng tại đây.</t>
         </is>
       </c>
     </row>
@@ -31388,7 +31388,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Stress Level hiện tại của bạn được hiển thị tại đây.</t>
+          <t>Mức Stress hiện tại của cậu được hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -31453,7 +31453,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Stress Level hiện tại của bạn được hiển thị tại đây.</t>
+          <t>Mức Stress hiện tại của cậu được hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -31518,7 +31518,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Stress Level hiện tại của bạn được hiển thị tại đây.</t>
+          <t>Mức Stress hiện tại của cậu được hiển thị tại đây.</t>
         </is>
       </c>
     </row>
@@ -31583,7 +31583,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Có thể trang bị thêm Stress Modules trong Disaster Trial để tăng độ khó.</t>
+          <t>Có thể trang bị thêm Mô-đun Áp lực trong Thử thách Tai ương để tăng độ khó.</t>
         </is>
       </c>
     </row>
@@ -31648,7 +31648,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Có thể trang bị thêm Stress Modules trong Disaster Trial để tăng độ khó.</t>
+          <t>Có thể trang bị thêm Mô-đun Áp lực trong Thử thách Tai ương để tăng độ khó.</t>
         </is>
       </c>
     </row>
@@ -31713,7 +31713,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Có thể trang bị thêm Stress Modules trong Disaster Trial để tăng độ khó.</t>
+          <t>Có thể trang bị thêm Mô-đun Áp lực trong Thử thách Tai ương để tăng độ khó.</t>
         </is>
       </c>
     </row>
@@ -31778,7 +31778,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>{0} Resonance Conversion unlocked.</t>
+          <t>Chuyển Đổi Cộng Hưởng đã mở khóa.</t>
         </is>
       </c>
     </row>
@@ -31843,7 +31843,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Đã mở khóa Resonance Conversion.</t>
+          <t>Chuyển Hóa Cộng Hưởng đã được mở khóa.</t>
         </is>
       </c>
     </row>
@@ -31908,7 +31908,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Chọn Rover</t>
+          <t>Chọn Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -31973,7 +31973,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Chọn Rover</t>
+          <t>Chọn Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -32038,7 +32038,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Chọn Rover</t>
+          <t>Chọn Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -32103,7 +32103,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Xem thuộc tính hiện tại của Rover</t>
+          <t>Xem Thuộc Tính Hiện Tại Của Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -32168,7 +32168,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Xem thuộc tính hiện tại của Rover</t>
+          <t>Xem Thuộc Tính Hiện Tại Của Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -32233,7 +32233,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Xem thuộc tính hiện tại của Rover</t>
+          <t>Xem Thuộc Tính Hiện Tại Của Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -32298,7 +32298,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Attribute Cộng hưởng của Rover có thể chuyển đổi giữa Spectro và Aero.</t>
+          <t>Thuộc tính Cộng Hưởng của Rover có thể chuyển đổi giữa Spectro và Aero.</t>
         </is>
       </c>
     </row>
@@ -32363,7 +32363,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Thuộc Tính Resonance của Rover có thể chuyển đổi giữa Spectro và Aero.</t>
+          <t>Thuộc tính Cộng Hưởng của Rover có thể chuyển đổi giữa Spectro và Aero.</t>
         </is>
       </c>
     </row>
@@ -32428,7 +32428,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Thuộc Tính Resonance của Rover có thể chuyển đổi giữa Spectro và Aero.</t>
+          <t>Thuộc tính Cộng Hưởng của Rover có thể chuyển đổi giữa Spectro và Aero.</t>
         </is>
       </c>
     </row>
@@ -32493,7 +32493,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>{0} Resonance Conversion unlocked.</t>
+          <t>Chuyển Đổi Cộng Hưởng đã mở khóa.</t>
         </is>
       </c>
     </row>
@@ -32558,7 +32558,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Đã mở khóa Resonance Conversion.</t>
+          <t>Chuyển Hóa Cộng Hưởng đã được mở khóa.</t>
         </is>
       </c>
     </row>
@@ -32623,7 +32623,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Chọn Rover</t>
+          <t>Chọn Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -32688,7 +32688,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Chọn Rover</t>
+          <t>Chọn Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -32753,7 +32753,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Chọn Rover</t>
+          <t>Chọn Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -32818,7 +32818,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Xem thuộc tính hiện tại của Rover</t>
+          <t>Xem Thuộc Tính Hiện Tại Của Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -32883,7 +32883,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Xem thuộc tính hiện tại của Rover</t>
+          <t>Xem Thuộc Tính Hiện Tại Của Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -32948,7 +32948,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Xem thuộc tính hiện tại của Rover</t>
+          <t>Xem Thuộc Tính Hiện Tại Của Vận Mệnh Giả</t>
         </is>
       </c>
     </row>
@@ -33013,7 +33013,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Thuộc Tính Resonance của Rover có thể chuyển đổi giữa Spectro và Aero.</t>
+          <t>Thuộc tính Cộng Hưởng của Rover có thể chuyển đổi giữa Spectro và Aero.</t>
         </is>
       </c>
     </row>
